--- a/datos/datos_calidad_aire_DIARIO.xlsx
+++ b/datos/datos_calidad_aire_DIARIO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73,7 +73,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -81,23 +81,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -596,1362 +587,1362 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_AGUA SANTA</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_AGUA SANTA</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_AGUA SANTA</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_AGUA SANTA</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_AGUA SANTA</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_AGUA SANTA</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_AGUA SANTA</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_AGUA SANTA</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_AGUA SANTA</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_AGUA SANTA</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_AGUA SANTA</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_AGUA SANTA</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_ATLIXCO</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_ATLIXCO</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_ATLIXCO</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_ATLIXCO</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_ATLIXCO</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_ATLIXCO</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_ATLIXCO</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_ATLIXCO</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_ATLIXCO</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_ATLIXCO</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_ATLIXCO</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_ATLIXCO</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_BINE</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_BINE</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_BINE</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_BINE</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_BINE</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_BINE</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_BINE</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AG1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_BINE</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AH1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_BINE</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AI1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_BINE</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AJ1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_BINE</t>
         </is>
       </c>
-      <c r="AK1" s="3" t="inlineStr">
+      <c r="AK1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_BINE</t>
         </is>
       </c>
-      <c r="AL1" s="3" t="inlineStr">
+      <c r="AL1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_NINFAS</t>
         </is>
       </c>
-      <c r="AM1" s="3" t="inlineStr">
+      <c r="AM1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_NINFAS</t>
         </is>
       </c>
-      <c r="AN1" s="3" t="inlineStr">
+      <c r="AN1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_NINFAS</t>
         </is>
       </c>
-      <c r="AO1" s="3" t="inlineStr">
+      <c r="AO1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_NINFAS</t>
         </is>
       </c>
-      <c r="AP1" s="3" t="inlineStr">
+      <c r="AP1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_NINFAS</t>
         </is>
       </c>
-      <c r="AQ1" s="3" t="inlineStr">
+      <c r="AQ1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_NINFAS</t>
         </is>
       </c>
-      <c r="AR1" s="3" t="inlineStr">
+      <c r="AR1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_NINFAS</t>
         </is>
       </c>
-      <c r="AS1" s="3" t="inlineStr">
+      <c r="AS1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_NINFAS</t>
         </is>
       </c>
-      <c r="AT1" s="3" t="inlineStr">
+      <c r="AT1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_NINFAS</t>
         </is>
       </c>
-      <c r="AU1" s="3" t="inlineStr">
+      <c r="AU1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_NINFAS</t>
         </is>
       </c>
-      <c r="AV1" s="3" t="inlineStr">
+      <c r="AV1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_NINFAS</t>
         </is>
       </c>
-      <c r="AW1" s="3" t="inlineStr">
+      <c r="AW1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_NINFAS</t>
         </is>
       </c>
-      <c r="AX1" s="3" t="inlineStr">
+      <c r="AX1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_TEHUACAN</t>
         </is>
       </c>
-      <c r="AY1" s="3" t="inlineStr">
+      <c r="AY1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_TEHUACAN</t>
         </is>
       </c>
-      <c r="AZ1" s="3" t="inlineStr">
+      <c r="AZ1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_TEHUACAN</t>
         </is>
       </c>
-      <c r="BA1" s="3" t="inlineStr">
+      <c r="BA1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_TEHUACAN</t>
         </is>
       </c>
-      <c r="BB1" s="3" t="inlineStr">
+      <c r="BB1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_TEHUACAN</t>
         </is>
       </c>
-      <c r="BC1" s="3" t="inlineStr">
+      <c r="BC1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_TEHUACAN</t>
         </is>
       </c>
-      <c r="BD1" s="3" t="inlineStr">
+      <c r="BD1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_TEHUACAN</t>
         </is>
       </c>
-      <c r="BE1" s="3" t="inlineStr">
+      <c r="BE1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_TEHUACAN</t>
         </is>
       </c>
-      <c r="BF1" s="3" t="inlineStr">
+      <c r="BF1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_TEHUACAN</t>
         </is>
       </c>
-      <c r="BG1" s="3" t="inlineStr">
+      <c r="BG1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_TEHUACAN</t>
         </is>
       </c>
-      <c r="BH1" s="3" t="inlineStr">
+      <c r="BH1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_TEHUACAN</t>
         </is>
       </c>
-      <c r="BI1" s="3" t="inlineStr">
+      <c r="BI1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_TEHUACAN</t>
         </is>
       </c>
-      <c r="BJ1" s="3" t="inlineStr">
+      <c r="BJ1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BK1" s="3" t="inlineStr">
+      <c r="BK1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BL1" s="3" t="inlineStr">
+      <c r="BL1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BM1" s="3" t="inlineStr">
+      <c r="BM1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BN1" s="3" t="inlineStr">
+      <c r="BN1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BO1" s="3" t="inlineStr">
+      <c r="BO1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BP1" s="3" t="inlineStr">
+      <c r="BP1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BQ1" s="3" t="inlineStr">
+      <c r="BQ1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BR1" s="3" t="inlineStr">
+      <c r="BR1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BS1" s="3" t="inlineStr">
+      <c r="BS1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BT1" s="3" t="inlineStr">
+      <c r="BT1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BU1" s="3" t="inlineStr">
+      <c r="BU1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BV1" s="3" t="inlineStr">
+      <c r="BV1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_UTP</t>
         </is>
       </c>
-      <c r="BW1" s="3" t="inlineStr">
+      <c r="BW1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_UTP</t>
         </is>
       </c>
-      <c r="BX1" s="3" t="inlineStr">
+      <c r="BX1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_UTP</t>
         </is>
       </c>
-      <c r="BY1" s="3" t="inlineStr">
+      <c r="BY1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_UTP</t>
         </is>
       </c>
-      <c r="BZ1" s="3" t="inlineStr">
+      <c r="BZ1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_UTP</t>
         </is>
       </c>
-      <c r="CA1" s="3" t="inlineStr">
+      <c r="CA1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_UTP</t>
         </is>
       </c>
-      <c r="CB1" s="3" t="inlineStr">
+      <c r="CB1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_UTP</t>
         </is>
       </c>
-      <c r="CC1" s="3" t="inlineStr">
+      <c r="CC1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_UTP</t>
         </is>
       </c>
-      <c r="CD1" s="3" t="inlineStr">
+      <c r="CD1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_UTP</t>
         </is>
       </c>
-      <c r="CE1" s="3" t="inlineStr">
+      <c r="CE1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_UTP</t>
         </is>
       </c>
-      <c r="CF1" s="3" t="inlineStr">
+      <c r="CF1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_UTP</t>
         </is>
       </c>
-      <c r="CG1" s="3" t="inlineStr">
+      <c r="CG1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_UTP</t>
         </is>
       </c>
-      <c r="CH1" s="3" t="inlineStr">
+      <c r="CH1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_VELODROMO</t>
         </is>
       </c>
-      <c r="CI1" s="3" t="inlineStr">
+      <c r="CI1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_VELODROMO</t>
         </is>
       </c>
-      <c r="CJ1" s="3" t="inlineStr">
+      <c r="CJ1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_VELODROMO</t>
         </is>
       </c>
-      <c r="CK1" s="3" t="inlineStr">
+      <c r="CK1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_VELODROMO</t>
         </is>
       </c>
-      <c r="CL1" s="3" t="inlineStr">
+      <c r="CL1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_VELODROMO</t>
         </is>
       </c>
-      <c r="CM1" s="3" t="inlineStr">
+      <c r="CM1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_VELODROMO</t>
         </is>
       </c>
-      <c r="CN1" s="3" t="inlineStr">
+      <c r="CN1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_VELODROMO</t>
         </is>
       </c>
-      <c r="CO1" s="3" t="inlineStr">
+      <c r="CO1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_VELODROMO</t>
         </is>
       </c>
-      <c r="CP1" s="3" t="inlineStr">
+      <c r="CP1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_VELODROMO</t>
         </is>
       </c>
-      <c r="CQ1" s="3" t="inlineStr">
+      <c r="CQ1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_VELODROMO</t>
         </is>
       </c>
-      <c r="CR1" s="3" t="inlineStr">
+      <c r="CR1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_VELODROMO</t>
         </is>
       </c>
-      <c r="CS1" s="3" t="inlineStr">
+      <c r="CS1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_VELODROMO</t>
         </is>
       </c>
-      <c r="CT1" s="3" t="inlineStr">
+      <c r="CT1" s="2" t="inlineStr">
         <is>
           <t>Calidad del aire</t>
         </is>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="3" t="n">
         <v>46054</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="n">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>0.057</v>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="n">
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>0.019</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="n">
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="n">
         <v>0.51</v>
       </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="n">
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="n">
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="M2" s="8" t="n">
+      <c r="M2" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="N2" s="10" t="inlineStr"/>
-      <c r="O2" s="10" t="inlineStr"/>
-      <c r="P2" s="10" t="inlineStr"/>
-      <c r="Q2" s="10" t="inlineStr"/>
-      <c r="R2" s="10" t="inlineStr"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="10" t="inlineStr"/>
-      <c r="U2" s="10" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="W2" s="7" t="n">
+      <c r="N2" s="9" t="inlineStr"/>
+      <c r="O2" s="9" t="inlineStr"/>
+      <c r="P2" s="9" t="inlineStr"/>
+      <c r="Q2" s="9" t="inlineStr"/>
+      <c r="R2" s="9" t="inlineStr"/>
+      <c r="S2" s="9" t="inlineStr"/>
+      <c r="T2" s="9" t="inlineStr"/>
+      <c r="U2" s="9" t="inlineStr"/>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="W2" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="X2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="Y2" s="7" t="n">
+      <c r="X2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="Y2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="inlineStr">
+      <c r="Z2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="AA2" s="6" t="n">
+      <c r="AA2" s="5" t="n">
         <v>0.061</v>
       </c>
-      <c r="AB2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AC2" s="6" t="n">
+      <c r="AB2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AC2" s="5" t="n">
         <v>0.019</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AE2" s="7" t="n">
+      <c r="AD2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AE2" s="6" t="n">
         <v>1.48</v>
       </c>
-      <c r="AF2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AG2" s="6" t="n">
+      <c r="AF2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AG2" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="AH2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AI2" s="8" t="n">
+      <c r="AH2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AI2" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="AJ2" s="9" t="inlineStr">
+      <c r="AJ2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="AK2" s="8" t="n">
+      <c r="AK2" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="AL2" s="10" t="inlineStr"/>
-      <c r="AM2" s="10" t="inlineStr"/>
-      <c r="AN2" s="10" t="inlineStr"/>
-      <c r="AO2" s="10" t="inlineStr"/>
-      <c r="AP2" s="10" t="inlineStr"/>
-      <c r="AQ2" s="10" t="inlineStr"/>
-      <c r="AR2" s="10" t="inlineStr"/>
-      <c r="AS2" s="10" t="inlineStr"/>
-      <c r="AT2" s="10" t="inlineStr"/>
-      <c r="AU2" s="10" t="inlineStr"/>
-      <c r="AV2" s="10" t="inlineStr"/>
-      <c r="AW2" s="10" t="inlineStr"/>
-      <c r="AX2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AY2" s="6" t="n">
+      <c r="AL2" s="9" t="inlineStr"/>
+      <c r="AM2" s="9" t="inlineStr"/>
+      <c r="AN2" s="9" t="inlineStr"/>
+      <c r="AO2" s="9" t="inlineStr"/>
+      <c r="AP2" s="9" t="inlineStr"/>
+      <c r="AQ2" s="9" t="inlineStr"/>
+      <c r="AR2" s="9" t="inlineStr"/>
+      <c r="AS2" s="9" t="inlineStr"/>
+      <c r="AT2" s="9" t="inlineStr"/>
+      <c r="AU2" s="9" t="inlineStr"/>
+      <c r="AV2" s="9" t="inlineStr"/>
+      <c r="AW2" s="9" t="inlineStr"/>
+      <c r="AX2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AY2" s="5" t="n">
         <v>0.029</v>
       </c>
-      <c r="AZ2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BA2" s="6" t="n">
+      <c r="AZ2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BA2" s="5" t="n">
         <v>0.023</v>
       </c>
-      <c r="BB2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BC2" s="6" t="n">
+      <c r="BB2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BC2" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="BD2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BE2" s="7" t="n">
+      <c r="BD2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BE2" s="6" t="n">
         <v>1.75</v>
       </c>
-      <c r="BF2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BG2" s="8" t="n">
+      <c r="BF2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BG2" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="BH2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BI2" s="8" t="n">
+      <c r="BH2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BI2" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="BJ2" s="11" t="inlineStr">
+      <c r="BJ2" s="10" t="inlineStr">
         <is>
           <t>Muy Mala</t>
         </is>
       </c>
-      <c r="BK2" s="6" t="n">
+      <c r="BK2" s="5" t="n">
         <v>0.144</v>
       </c>
-      <c r="BL2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BM2" s="6" t="n">
+      <c r="BL2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BM2" s="5" t="n">
         <v>0.024</v>
       </c>
-      <c r="BN2" s="10" t="inlineStr"/>
-      <c r="BO2" s="10" t="inlineStr"/>
-      <c r="BP2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BQ2" s="7" t="n">
+      <c r="BN2" s="9" t="inlineStr"/>
+      <c r="BO2" s="9" t="inlineStr"/>
+      <c r="BP2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BQ2" s="6" t="n">
         <v>0.65</v>
       </c>
-      <c r="BR2" s="9" t="inlineStr">
+      <c r="BR2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="BS2" s="8" t="n">
+      <c r="BS2" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="BT2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BU2" s="8" t="n">
+      <c r="BT2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BU2" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="BV2" s="9" t="inlineStr">
+      <c r="BV2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="BW2" s="6" t="n">
+      <c r="BW2" s="5" t="n">
         <v>0.061</v>
       </c>
-      <c r="BX2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BY2" s="6" t="n">
+      <c r="BX2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BY2" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="BZ2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CA2" s="7" t="n">
+      <c r="BZ2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CA2" s="6" t="n">
         <v>0.65</v>
       </c>
-      <c r="CB2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CC2" s="6" t="n">
+      <c r="CB2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CC2" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="CD2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CE2" s="8" t="n">
+      <c r="CD2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CE2" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="CF2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CG2" s="8" t="n">
+      <c r="CF2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CG2" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="CH2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CI2" s="6" t="n">
+      <c r="CH2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CI2" s="5" t="n">
         <v>0.054</v>
       </c>
-      <c r="CJ2" s="10" t="inlineStr"/>
-      <c r="CK2" s="10" t="inlineStr"/>
-      <c r="CL2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CM2" s="7" t="n">
+      <c r="CJ2" s="9" t="inlineStr"/>
+      <c r="CK2" s="9" t="inlineStr"/>
+      <c r="CL2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CM2" s="6" t="n">
         <v>0.68</v>
       </c>
-      <c r="CN2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CO2" s="6" t="n">
+      <c r="CN2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CO2" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="CP2" s="12" t="inlineStr">
+      <c r="CP2" s="11" t="inlineStr">
         <is>
           <t>Mala</t>
         </is>
       </c>
-      <c r="CQ2" s="8" t="n">
+      <c r="CQ2" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="CR2" s="10" t="inlineStr"/>
-      <c r="CS2" s="10" t="inlineStr"/>
-      <c r="CT2" s="11" t="inlineStr">
+      <c r="CR2" s="9" t="inlineStr"/>
+      <c r="CS2" s="9" t="inlineStr"/>
+      <c r="CT2" s="10" t="inlineStr">
         <is>
           <t>Muy Mala</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="3" t="n">
         <v>46055</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="5" t="n">
         <v>0.074</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
         <v>0.022</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="n">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>0.54</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="n">
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="n">
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="N3" s="10" t="inlineStr"/>
-      <c r="O3" s="10" t="inlineStr"/>
-      <c r="P3" s="10" t="inlineStr"/>
-      <c r="Q3" s="10" t="inlineStr"/>
-      <c r="R3" s="10" t="inlineStr"/>
-      <c r="S3" s="10" t="inlineStr"/>
-      <c r="T3" s="10" t="inlineStr"/>
-      <c r="U3" s="10" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="W3" s="7" t="n">
+      <c r="N3" s="9" t="inlineStr"/>
+      <c r="O3" s="9" t="inlineStr"/>
+      <c r="P3" s="9" t="inlineStr"/>
+      <c r="Q3" s="9" t="inlineStr"/>
+      <c r="R3" s="9" t="inlineStr"/>
+      <c r="S3" s="9" t="inlineStr"/>
+      <c r="T3" s="9" t="inlineStr"/>
+      <c r="U3" s="9" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="X3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="Y3" s="7" t="n">
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="Y3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="inlineStr">
+      <c r="Z3" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="AA3" s="6" t="n">
+      <c r="AA3" s="5" t="n">
         <v>0.079</v>
       </c>
-      <c r="AB3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AC3" s="6" t="n">
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AC3" s="5" t="n">
         <v>0.027</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AE3" s="7" t="n">
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AE3" s="6" t="n">
         <v>1.52</v>
       </c>
-      <c r="AF3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AG3" s="6" t="n">
+      <c r="AF3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AG3" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="AH3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AI3" s="8" t="n">
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AI3" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="AJ3" s="9" t="inlineStr">
+      <c r="AJ3" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="AK3" s="8" t="n">
+      <c r="AK3" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="AL3" s="10" t="inlineStr"/>
-      <c r="AM3" s="10" t="inlineStr"/>
-      <c r="AN3" s="10" t="inlineStr"/>
-      <c r="AO3" s="10" t="inlineStr"/>
-      <c r="AP3" s="10" t="inlineStr"/>
-      <c r="AQ3" s="10" t="inlineStr"/>
-      <c r="AR3" s="10" t="inlineStr"/>
-      <c r="AS3" s="10" t="inlineStr"/>
-      <c r="AT3" s="10" t="inlineStr"/>
-      <c r="AU3" s="10" t="inlineStr"/>
-      <c r="AV3" s="10" t="inlineStr"/>
-      <c r="AW3" s="10" t="inlineStr"/>
-      <c r="AX3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AY3" s="6" t="n">
+      <c r="AL3" s="9" t="inlineStr"/>
+      <c r="AM3" s="9" t="inlineStr"/>
+      <c r="AN3" s="9" t="inlineStr"/>
+      <c r="AO3" s="9" t="inlineStr"/>
+      <c r="AP3" s="9" t="inlineStr"/>
+      <c r="AQ3" s="9" t="inlineStr"/>
+      <c r="AR3" s="9" t="inlineStr"/>
+      <c r="AS3" s="9" t="inlineStr"/>
+      <c r="AT3" s="9" t="inlineStr"/>
+      <c r="AU3" s="9" t="inlineStr"/>
+      <c r="AV3" s="9" t="inlineStr"/>
+      <c r="AW3" s="9" t="inlineStr"/>
+      <c r="AX3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AY3" s="5" t="n">
         <v>0.025</v>
       </c>
-      <c r="AZ3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BA3" s="6" t="n">
+      <c r="AZ3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BA3" s="5" t="n">
         <v>0.036</v>
       </c>
-      <c r="BB3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BC3" s="6" t="n">
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BC3" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="BD3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BE3" s="7" t="n">
+      <c r="BD3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BE3" s="6" t="n">
         <v>1.85</v>
       </c>
-      <c r="BF3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BG3" s="8" t="n">
+      <c r="BF3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BG3" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="BH3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BI3" s="8" t="n">
+      <c r="BH3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BI3" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="BJ3" s="9" t="inlineStr">
+      <c r="BJ3" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="BK3" s="6" t="n">
+      <c r="BK3" s="5" t="n">
         <v>0.066</v>
       </c>
-      <c r="BL3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BM3" s="6" t="n">
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BM3" s="5" t="n">
         <v>0.032</v>
       </c>
-      <c r="BN3" s="10" t="inlineStr"/>
-      <c r="BO3" s="10" t="inlineStr"/>
-      <c r="BP3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BQ3" s="7" t="n">
+      <c r="BN3" s="9" t="inlineStr"/>
+      <c r="BO3" s="9" t="inlineStr"/>
+      <c r="BP3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BQ3" s="6" t="n">
         <v>0.73</v>
       </c>
-      <c r="BR3" s="9" t="inlineStr">
+      <c r="BR3" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="BS3" s="8" t="n">
+      <c r="BS3" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="BT3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BU3" s="8" t="n">
+      <c r="BT3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BU3" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="BV3" s="9" t="inlineStr">
+      <c r="BV3" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="BW3" s="6" t="n">
+      <c r="BW3" s="5" t="n">
         <v>0.073</v>
       </c>
-      <c r="BX3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BY3" s="6" t="n">
+      <c r="BX3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BY3" s="5" t="n">
         <v>0.022</v>
       </c>
-      <c r="BZ3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CA3" s="7" t="n">
+      <c r="BZ3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CA3" s="6" t="n">
         <v>0.73</v>
       </c>
-      <c r="CB3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CC3" s="6" t="n">
+      <c r="CB3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CC3" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="CD3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CE3" s="8" t="n">
+      <c r="CD3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CE3" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="CF3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CG3" s="8" t="n">
+      <c r="CF3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CG3" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="CH3" s="9" t="inlineStr">
+      <c r="CH3" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="CI3" s="6" t="n">
+      <c r="CI3" s="5" t="n">
         <v>0.063</v>
       </c>
-      <c r="CJ3" s="10" t="inlineStr"/>
-      <c r="CK3" s="10" t="inlineStr"/>
-      <c r="CL3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CM3" s="7" t="n">
+      <c r="CJ3" s="9" t="inlineStr"/>
+      <c r="CK3" s="9" t="inlineStr"/>
+      <c r="CL3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CM3" s="6" t="n">
         <v>0.78</v>
       </c>
-      <c r="CN3" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CO3" s="6" t="n">
+      <c r="CN3" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CO3" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="CP3" s="12" t="inlineStr">
+      <c r="CP3" s="11" t="inlineStr">
         <is>
           <t>Mala</t>
         </is>
       </c>
-      <c r="CQ3" s="8" t="n">
+      <c r="CQ3" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="CR3" s="10" t="inlineStr"/>
-      <c r="CS3" s="10" t="inlineStr"/>
-      <c r="CT3" s="12" t="inlineStr">
+      <c r="CR3" s="9" t="inlineStr"/>
+      <c r="CS3" s="9" t="inlineStr"/>
+      <c r="CT3" s="11" t="inlineStr">
         <is>
           <t>Mala</t>
         </is>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="3" t="n">
         <v>46056</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>0.047</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>0.026</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="n">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="n">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr"/>
-      <c r="L4" s="10" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="10" t="inlineStr"/>
-      <c r="O4" s="10" t="inlineStr"/>
-      <c r="P4" s="10" t="inlineStr"/>
-      <c r="Q4" s="10" t="inlineStr"/>
-      <c r="R4" s="10" t="inlineStr"/>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="10" t="inlineStr"/>
-      <c r="U4" s="10" t="inlineStr"/>
-      <c r="V4" s="10" t="inlineStr"/>
-      <c r="W4" s="10" t="inlineStr"/>
-      <c r="X4" s="10" t="inlineStr"/>
-      <c r="Y4" s="10" t="inlineStr"/>
-      <c r="Z4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AA4" s="6" t="n">
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr"/>
+      <c r="L4" s="9" t="inlineStr"/>
+      <c r="M4" s="9" t="inlineStr"/>
+      <c r="N4" s="9" t="inlineStr"/>
+      <c r="O4" s="9" t="inlineStr"/>
+      <c r="P4" s="9" t="inlineStr"/>
+      <c r="Q4" s="9" t="inlineStr"/>
+      <c r="R4" s="9" t="inlineStr"/>
+      <c r="S4" s="9" t="inlineStr"/>
+      <c r="T4" s="9" t="inlineStr"/>
+      <c r="U4" s="9" t="inlineStr"/>
+      <c r="V4" s="9" t="inlineStr"/>
+      <c r="W4" s="9" t="inlineStr"/>
+      <c r="X4" s="9" t="inlineStr"/>
+      <c r="Y4" s="9" t="inlineStr"/>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="n">
         <v>0.043</v>
       </c>
-      <c r="AB4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AC4" s="6" t="n">
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AC4" s="5" t="n">
         <v>0.029</v>
       </c>
-      <c r="AD4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AE4" s="7" t="n">
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AE4" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="AF4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AG4" s="6" t="n">
+      <c r="AF4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AG4" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="AH4" s="10" t="inlineStr"/>
-      <c r="AI4" s="10" t="inlineStr"/>
-      <c r="AJ4" s="10" t="inlineStr"/>
-      <c r="AK4" s="10" t="inlineStr"/>
-      <c r="AL4" s="10" t="inlineStr"/>
-      <c r="AM4" s="10" t="inlineStr"/>
-      <c r="AN4" s="10" t="inlineStr"/>
-      <c r="AO4" s="10" t="inlineStr"/>
-      <c r="AP4" s="10" t="inlineStr"/>
-      <c r="AQ4" s="10" t="inlineStr"/>
-      <c r="AR4" s="10" t="inlineStr"/>
-      <c r="AS4" s="10" t="inlineStr"/>
-      <c r="AT4" s="10" t="inlineStr"/>
-      <c r="AU4" s="10" t="inlineStr"/>
-      <c r="AV4" s="10" t="inlineStr"/>
-      <c r="AW4" s="10" t="inlineStr"/>
-      <c r="AX4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AY4" s="6" t="n">
+      <c r="AH4" s="9" t="inlineStr"/>
+      <c r="AI4" s="9" t="inlineStr"/>
+      <c r="AJ4" s="9" t="inlineStr"/>
+      <c r="AK4" s="9" t="inlineStr"/>
+      <c r="AL4" s="9" t="inlineStr"/>
+      <c r="AM4" s="9" t="inlineStr"/>
+      <c r="AN4" s="9" t="inlineStr"/>
+      <c r="AO4" s="9" t="inlineStr"/>
+      <c r="AP4" s="9" t="inlineStr"/>
+      <c r="AQ4" s="9" t="inlineStr"/>
+      <c r="AR4" s="9" t="inlineStr"/>
+      <c r="AS4" s="9" t="inlineStr"/>
+      <c r="AT4" s="9" t="inlineStr"/>
+      <c r="AU4" s="9" t="inlineStr"/>
+      <c r="AV4" s="9" t="inlineStr"/>
+      <c r="AW4" s="9" t="inlineStr"/>
+      <c r="AX4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AY4" s="5" t="n">
         <v>0.022</v>
       </c>
-      <c r="AZ4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BA4" s="6" t="n">
+      <c r="AZ4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BA4" s="5" t="n">
         <v>0.029</v>
       </c>
-      <c r="BB4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BC4" s="6" t="n">
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BC4" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="BD4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BE4" s="7" t="n">
+      <c r="BD4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BE4" s="6" t="n">
         <v>1.95</v>
       </c>
-      <c r="BF4" s="10" t="inlineStr"/>
-      <c r="BG4" s="10" t="inlineStr"/>
-      <c r="BH4" s="10" t="inlineStr"/>
-      <c r="BI4" s="10" t="inlineStr"/>
-      <c r="BJ4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BK4" s="6" t="n">
+      <c r="BF4" s="9" t="inlineStr"/>
+      <c r="BG4" s="9" t="inlineStr"/>
+      <c r="BH4" s="9" t="inlineStr"/>
+      <c r="BI4" s="9" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BK4" s="5" t="n">
         <v>0.043</v>
       </c>
-      <c r="BL4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BM4" s="6" t="n">
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BM4" s="5" t="n">
         <v>0.023</v>
       </c>
-      <c r="BN4" s="10" t="inlineStr"/>
-      <c r="BO4" s="10" t="inlineStr"/>
-      <c r="BP4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BQ4" s="7" t="n">
+      <c r="BN4" s="9" t="inlineStr"/>
+      <c r="BO4" s="9" t="inlineStr"/>
+      <c r="BP4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BQ4" s="6" t="n">
         <v>0.75</v>
       </c>
-      <c r="BR4" s="10" t="inlineStr"/>
-      <c r="BS4" s="10" t="inlineStr"/>
-      <c r="BT4" s="10" t="inlineStr"/>
-      <c r="BU4" s="10" t="inlineStr"/>
-      <c r="BV4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BW4" s="6" t="n">
+      <c r="BR4" s="9" t="inlineStr"/>
+      <c r="BS4" s="9" t="inlineStr"/>
+      <c r="BT4" s="9" t="inlineStr"/>
+      <c r="BU4" s="9" t="inlineStr"/>
+      <c r="BV4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BW4" s="5" t="n">
         <v>0.052</v>
       </c>
-      <c r="BX4" s="9" t="inlineStr">
+      <c r="BX4" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="BY4" s="6" t="n">
+      <c r="BY4" s="5" t="n">
         <v>0.066</v>
       </c>
-      <c r="BZ4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CA4" s="7" t="n">
+      <c r="BZ4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CA4" s="6" t="n">
         <v>1.56</v>
       </c>
-      <c r="CB4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CC4" s="6" t="n">
+      <c r="CB4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CC4" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="CD4" s="10" t="inlineStr"/>
-      <c r="CE4" s="10" t="inlineStr"/>
-      <c r="CF4" s="10" t="inlineStr"/>
-      <c r="CG4" s="10" t="inlineStr"/>
-      <c r="CH4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CI4" s="6" t="n">
+      <c r="CD4" s="9" t="inlineStr"/>
+      <c r="CE4" s="9" t="inlineStr"/>
+      <c r="CF4" s="9" t="inlineStr"/>
+      <c r="CG4" s="9" t="inlineStr"/>
+      <c r="CH4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CI4" s="5" t="n">
         <v>0.034</v>
       </c>
-      <c r="CJ4" s="10" t="inlineStr"/>
-      <c r="CK4" s="10" t="inlineStr"/>
-      <c r="CL4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CM4" s="7" t="n">
+      <c r="CJ4" s="9" t="inlineStr"/>
+      <c r="CK4" s="9" t="inlineStr"/>
+      <c r="CL4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CM4" s="6" t="n">
         <v>1.19</v>
       </c>
-      <c r="CN4" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CO4" s="6" t="n">
+      <c r="CN4" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CO4" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="CP4" s="10" t="inlineStr"/>
-      <c r="CQ4" s="10" t="inlineStr"/>
-      <c r="CR4" s="10" t="inlineStr"/>
-      <c r="CS4" s="10" t="inlineStr"/>
-      <c r="CT4" s="9" t="inlineStr">
+      <c r="CP4" s="9" t="inlineStr"/>
+      <c r="CQ4" s="9" t="inlineStr"/>
+      <c r="CR4" s="9" t="inlineStr"/>
+      <c r="CS4" s="9" t="inlineStr"/>
+      <c r="CT4" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -2072,694 +2063,694 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_AGUA SANTA</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_AGUA SANTA</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_AGUA SANTA</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_AGUA SANTA</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_AGUA SANTA</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_AGUA SANTA</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_AGUA SANTA</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_AGUA SANTA</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_AGUA SANTA</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_AGUA SANTA</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_AGUA SANTA</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_AGUA SANTA</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_ATLIXCO</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_ATLIXCO</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_ATLIXCO</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_ATLIXCO</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_ATLIXCO</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_ATLIXCO</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_ATLIXCO</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_ATLIXCO</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_ATLIXCO</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_ATLIXCO</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_ATLIXCO</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_ATLIXCO</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_BINE</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_BINE</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_BINE</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_BINE</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_BINE</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_BINE</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_BINE</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AG1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_BINE</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AH1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_BINE</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AI1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_BINE</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AJ1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_BINE</t>
         </is>
       </c>
-      <c r="AK1" s="3" t="inlineStr">
+      <c r="AK1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_BINE</t>
         </is>
       </c>
-      <c r="AL1" s="3" t="inlineStr">
+      <c r="AL1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_NINFAS</t>
         </is>
       </c>
-      <c r="AM1" s="3" t="inlineStr">
+      <c r="AM1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_NINFAS</t>
         </is>
       </c>
-      <c r="AN1" s="3" t="inlineStr">
+      <c r="AN1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_NINFAS</t>
         </is>
       </c>
-      <c r="AO1" s="3" t="inlineStr">
+      <c r="AO1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_NINFAS</t>
         </is>
       </c>
-      <c r="AP1" s="3" t="inlineStr">
+      <c r="AP1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_NINFAS</t>
         </is>
       </c>
-      <c r="AQ1" s="3" t="inlineStr">
+      <c r="AQ1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_NINFAS</t>
         </is>
       </c>
-      <c r="AR1" s="3" t="inlineStr">
+      <c r="AR1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_NINFAS</t>
         </is>
       </c>
-      <c r="AS1" s="3" t="inlineStr">
+      <c r="AS1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_NINFAS</t>
         </is>
       </c>
-      <c r="AT1" s="3" t="inlineStr">
+      <c r="AT1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_NINFAS</t>
         </is>
       </c>
-      <c r="AU1" s="3" t="inlineStr">
+      <c r="AU1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_NINFAS</t>
         </is>
       </c>
-      <c r="AV1" s="3" t="inlineStr">
+      <c r="AV1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_NINFAS</t>
         </is>
       </c>
-      <c r="AW1" s="3" t="inlineStr">
+      <c r="AW1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_NINFAS</t>
         </is>
       </c>
-      <c r="AX1" s="3" t="inlineStr">
+      <c r="AX1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_TEHUACAN</t>
         </is>
       </c>
-      <c r="AY1" s="3" t="inlineStr">
+      <c r="AY1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_TEHUACAN</t>
         </is>
       </c>
-      <c r="AZ1" s="3" t="inlineStr">
+      <c r="AZ1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_TEHUACAN</t>
         </is>
       </c>
-      <c r="BA1" s="3" t="inlineStr">
+      <c r="BA1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_TEHUACAN</t>
         </is>
       </c>
-      <c r="BB1" s="3" t="inlineStr">
+      <c r="BB1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_TEHUACAN</t>
         </is>
       </c>
-      <c r="BC1" s="3" t="inlineStr">
+      <c r="BC1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_TEHUACAN</t>
         </is>
       </c>
-      <c r="BD1" s="3" t="inlineStr">
+      <c r="BD1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_TEHUACAN</t>
         </is>
       </c>
-      <c r="BE1" s="3" t="inlineStr">
+      <c r="BE1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_TEHUACAN</t>
         </is>
       </c>
-      <c r="BF1" s="3" t="inlineStr">
+      <c r="BF1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_TEHUACAN</t>
         </is>
       </c>
-      <c r="BG1" s="3" t="inlineStr">
+      <c r="BG1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_TEHUACAN</t>
         </is>
       </c>
-      <c r="BH1" s="3" t="inlineStr">
+      <c r="BH1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_TEHUACAN</t>
         </is>
       </c>
-      <c r="BI1" s="3" t="inlineStr">
+      <c r="BI1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_TEHUACAN</t>
         </is>
       </c>
-      <c r="BJ1" s="3" t="inlineStr">
+      <c r="BJ1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BK1" s="3" t="inlineStr">
+      <c r="BK1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BL1" s="3" t="inlineStr">
+      <c r="BL1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BM1" s="3" t="inlineStr">
+      <c r="BM1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BN1" s="3" t="inlineStr">
+      <c r="BN1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BO1" s="3" t="inlineStr">
+      <c r="BO1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BP1" s="3" t="inlineStr">
+      <c r="BP1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BQ1" s="3" t="inlineStr">
+      <c r="BQ1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BR1" s="3" t="inlineStr">
+      <c r="BR1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BS1" s="3" t="inlineStr">
+      <c r="BS1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BT1" s="3" t="inlineStr">
+      <c r="BT1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BU1" s="3" t="inlineStr">
+      <c r="BU1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_TEXMELUCAN</t>
         </is>
       </c>
-      <c r="BV1" s="3" t="inlineStr">
+      <c r="BV1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_UTP</t>
         </is>
       </c>
-      <c r="BW1" s="3" t="inlineStr">
+      <c r="BW1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_UTP</t>
         </is>
       </c>
-      <c r="BX1" s="3" t="inlineStr">
+      <c r="BX1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_UTP</t>
         </is>
       </c>
-      <c r="BY1" s="3" t="inlineStr">
+      <c r="BY1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_UTP</t>
         </is>
       </c>
-      <c r="BZ1" s="3" t="inlineStr">
+      <c r="BZ1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_UTP</t>
         </is>
       </c>
-      <c r="CA1" s="3" t="inlineStr">
+      <c r="CA1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_UTP</t>
         </is>
       </c>
-      <c r="CB1" s="3" t="inlineStr">
+      <c r="CB1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_UTP</t>
         </is>
       </c>
-      <c r="CC1" s="3" t="inlineStr">
+      <c r="CC1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_UTP</t>
         </is>
       </c>
-      <c r="CD1" s="3" t="inlineStr">
+      <c r="CD1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_UTP</t>
         </is>
       </c>
-      <c r="CE1" s="3" t="inlineStr">
+      <c r="CE1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_UTP</t>
         </is>
       </c>
-      <c r="CF1" s="3" t="inlineStr">
+      <c r="CF1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_UTP</t>
         </is>
       </c>
-      <c r="CG1" s="3" t="inlineStr">
+      <c r="CG1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_UTP</t>
         </is>
       </c>
-      <c r="CH1" s="3" t="inlineStr">
+      <c r="CH1" s="2" t="inlineStr">
         <is>
           <t>AIRE_O3_VELODROMO</t>
         </is>
       </c>
-      <c r="CI1" s="3" t="inlineStr">
+      <c r="CI1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_O3_VELODROMO</t>
         </is>
       </c>
-      <c r="CJ1" s="3" t="inlineStr">
+      <c r="CJ1" s="2" t="inlineStr">
         <is>
           <t>AIRE_NO2_VELODROMO</t>
         </is>
       </c>
-      <c r="CK1" s="3" t="inlineStr">
+      <c r="CK1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_NO2_VELODROMO</t>
         </is>
       </c>
-      <c r="CL1" s="3" t="inlineStr">
+      <c r="CL1" s="2" t="inlineStr">
         <is>
           <t>AIRE_CO_VELODROMO</t>
         </is>
       </c>
-      <c r="CM1" s="3" t="inlineStr">
+      <c r="CM1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_CO_VELODROMO</t>
         </is>
       </c>
-      <c r="CN1" s="3" t="inlineStr">
+      <c r="CN1" s="2" t="inlineStr">
         <is>
           <t>AIRE_SO2_VELODROMO</t>
         </is>
       </c>
-      <c r="CO1" s="3" t="inlineStr">
+      <c r="CO1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_SO2_VELODROMO</t>
         </is>
       </c>
-      <c r="CP1" s="3" t="inlineStr">
+      <c r="CP1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM10_VELODROMO</t>
         </is>
       </c>
-      <c r="CQ1" s="3" t="inlineStr">
+      <c r="CQ1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM10_VELODROMO</t>
         </is>
       </c>
-      <c r="CR1" s="3" t="inlineStr">
+      <c r="CR1" s="2" t="inlineStr">
         <is>
           <t>AIRE_PM2.5_VELODROMO</t>
         </is>
       </c>
-      <c r="CS1" s="3" t="inlineStr">
+      <c r="CS1" s="2" t="inlineStr">
         <is>
           <t>CANTIDAD_PM2.5_VELODROMO</t>
         </is>
       </c>
-      <c r="CT1" s="3" t="inlineStr">
+      <c r="CT1" s="2" t="inlineStr">
         <is>
           <t>Calidad del aire</t>
         </is>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="3" t="n">
         <v>46056</v>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="5" t="n">
         <v>0.078</v>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="n">
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>0.008</v>
       </c>
-      <c r="F2" s="10" t="inlineStr"/>
-      <c r="G2" s="10" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="n">
+      <c r="F2" s="9" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr"/>
-      <c r="L2" s="10" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
-      <c r="O2" s="10" t="inlineStr"/>
-      <c r="P2" s="10" t="inlineStr"/>
-      <c r="Q2" s="10" t="inlineStr"/>
-      <c r="R2" s="10" t="inlineStr"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="10" t="inlineStr"/>
-      <c r="U2" s="10" t="inlineStr"/>
-      <c r="V2" s="10" t="inlineStr"/>
-      <c r="W2" s="10" t="inlineStr"/>
-      <c r="X2" s="10" t="inlineStr"/>
-      <c r="Y2" s="10" t="inlineStr"/>
-      <c r="Z2" s="9" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr"/>
+      <c r="K2" s="9" t="inlineStr"/>
+      <c r="L2" s="9" t="inlineStr"/>
+      <c r="M2" s="9" t="inlineStr"/>
+      <c r="N2" s="9" t="inlineStr"/>
+      <c r="O2" s="9" t="inlineStr"/>
+      <c r="P2" s="9" t="inlineStr"/>
+      <c r="Q2" s="9" t="inlineStr"/>
+      <c r="R2" s="9" t="inlineStr"/>
+      <c r="S2" s="9" t="inlineStr"/>
+      <c r="T2" s="9" t="inlineStr"/>
+      <c r="U2" s="9" t="inlineStr"/>
+      <c r="V2" s="9" t="inlineStr"/>
+      <c r="W2" s="9" t="inlineStr"/>
+      <c r="X2" s="9" t="inlineStr"/>
+      <c r="Y2" s="9" t="inlineStr"/>
+      <c r="Z2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="AA2" s="6" t="n">
+      <c r="AA2" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="AB2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AC2" s="6" t="n">
+      <c r="AB2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AC2" s="5" t="n">
         <v>0.012</v>
       </c>
-      <c r="AD2" s="10" t="inlineStr"/>
-      <c r="AE2" s="10" t="inlineStr"/>
-      <c r="AF2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AG2" s="6" t="n">
+      <c r="AD2" s="9" t="inlineStr"/>
+      <c r="AE2" s="9" t="inlineStr"/>
+      <c r="AF2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AG2" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="AH2" s="10" t="inlineStr"/>
-      <c r="AI2" s="10" t="inlineStr"/>
-      <c r="AJ2" s="10" t="inlineStr"/>
-      <c r="AK2" s="10" t="inlineStr"/>
-      <c r="AL2" s="10" t="inlineStr"/>
-      <c r="AM2" s="10" t="inlineStr"/>
-      <c r="AN2" s="10" t="inlineStr"/>
-      <c r="AO2" s="10" t="inlineStr"/>
-      <c r="AP2" s="10" t="inlineStr"/>
-      <c r="AQ2" s="10" t="inlineStr"/>
-      <c r="AR2" s="10" t="inlineStr"/>
-      <c r="AS2" s="10" t="inlineStr"/>
-      <c r="AT2" s="10" t="inlineStr"/>
-      <c r="AU2" s="10" t="inlineStr"/>
-      <c r="AV2" s="10" t="inlineStr"/>
-      <c r="AW2" s="10" t="inlineStr"/>
-      <c r="AX2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="AY2" s="6" t="n">
+      <c r="AH2" s="9" t="inlineStr"/>
+      <c r="AI2" s="9" t="inlineStr"/>
+      <c r="AJ2" s="9" t="inlineStr"/>
+      <c r="AK2" s="9" t="inlineStr"/>
+      <c r="AL2" s="9" t="inlineStr"/>
+      <c r="AM2" s="9" t="inlineStr"/>
+      <c r="AN2" s="9" t="inlineStr"/>
+      <c r="AO2" s="9" t="inlineStr"/>
+      <c r="AP2" s="9" t="inlineStr"/>
+      <c r="AQ2" s="9" t="inlineStr"/>
+      <c r="AR2" s="9" t="inlineStr"/>
+      <c r="AS2" s="9" t="inlineStr"/>
+      <c r="AT2" s="9" t="inlineStr"/>
+      <c r="AU2" s="9" t="inlineStr"/>
+      <c r="AV2" s="9" t="inlineStr"/>
+      <c r="AW2" s="9" t="inlineStr"/>
+      <c r="AX2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="AY2" s="5" t="n">
         <v>0.029</v>
       </c>
-      <c r="AZ2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BA2" s="6" t="n">
+      <c r="AZ2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BA2" s="5" t="n">
         <v>0.017</v>
       </c>
-      <c r="BB2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BC2" s="6" t="n">
+      <c r="BB2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BC2" s="5" t="n">
         <v>0.002</v>
       </c>
-      <c r="BD2" s="10" t="inlineStr"/>
-      <c r="BE2" s="10" t="inlineStr"/>
-      <c r="BF2" s="10" t="inlineStr"/>
-      <c r="BG2" s="10" t="inlineStr"/>
-      <c r="BH2" s="10" t="inlineStr"/>
-      <c r="BI2" s="10" t="inlineStr"/>
-      <c r="BJ2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BK2" s="6" t="n">
+      <c r="BD2" s="9" t="inlineStr"/>
+      <c r="BE2" s="9" t="inlineStr"/>
+      <c r="BF2" s="9" t="inlineStr"/>
+      <c r="BG2" s="9" t="inlineStr"/>
+      <c r="BH2" s="9" t="inlineStr"/>
+      <c r="BI2" s="9" t="inlineStr"/>
+      <c r="BJ2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BK2" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="BL2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BM2" s="6" t="n">
+      <c r="BL2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BM2" s="5" t="n">
         <v>0.006</v>
       </c>
-      <c r="BN2" s="10" t="inlineStr"/>
-      <c r="BO2" s="10" t="inlineStr"/>
-      <c r="BP2" s="10" t="inlineStr"/>
-      <c r="BQ2" s="10" t="inlineStr"/>
-      <c r="BR2" s="10" t="inlineStr"/>
-      <c r="BS2" s="10" t="inlineStr"/>
-      <c r="BT2" s="10" t="inlineStr"/>
-      <c r="BU2" s="10" t="inlineStr"/>
-      <c r="BV2" s="9" t="inlineStr">
+      <c r="BN2" s="9" t="inlineStr"/>
+      <c r="BO2" s="9" t="inlineStr"/>
+      <c r="BP2" s="9" t="inlineStr"/>
+      <c r="BQ2" s="9" t="inlineStr"/>
+      <c r="BR2" s="9" t="inlineStr"/>
+      <c r="BS2" s="9" t="inlineStr"/>
+      <c r="BT2" s="9" t="inlineStr"/>
+      <c r="BU2" s="9" t="inlineStr"/>
+      <c r="BV2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="BW2" s="6" t="n">
+      <c r="BW2" s="5" t="n">
         <v>0.076</v>
       </c>
-      <c r="BX2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="BY2" s="6" t="n">
+      <c r="BX2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BY2" s="5" t="n">
         <v>0.011</v>
       </c>
-      <c r="BZ2" s="10" t="inlineStr"/>
-      <c r="CA2" s="10" t="inlineStr"/>
-      <c r="CB2" s="9" t="inlineStr">
+      <c r="BZ2" s="9" t="inlineStr"/>
+      <c r="CA2" s="9" t="inlineStr"/>
+      <c r="CB2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="CC2" s="6" t="n">
+      <c r="CC2" s="5" t="n">
         <v>0.058</v>
       </c>
-      <c r="CD2" s="10" t="inlineStr"/>
-      <c r="CE2" s="10" t="inlineStr"/>
-      <c r="CF2" s="10" t="inlineStr"/>
-      <c r="CG2" s="10" t="inlineStr"/>
-      <c r="CH2" s="9" t="inlineStr">
+      <c r="CD2" s="9" t="inlineStr"/>
+      <c r="CE2" s="9" t="inlineStr"/>
+      <c r="CF2" s="9" t="inlineStr"/>
+      <c r="CG2" s="9" t="inlineStr"/>
+      <c r="CH2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="CI2" s="6" t="n">
+      <c r="CI2" s="5" t="n">
         <v>0.063</v>
       </c>
-      <c r="CJ2" s="10" t="inlineStr"/>
-      <c r="CK2" s="10" t="inlineStr"/>
-      <c r="CL2" s="10" t="inlineStr"/>
-      <c r="CM2" s="10" t="inlineStr"/>
-      <c r="CN2" s="5" t="inlineStr">
-        <is>
-          <t>Buena</t>
-        </is>
-      </c>
-      <c r="CO2" s="6" t="n">
+      <c r="CJ2" s="9" t="inlineStr"/>
+      <c r="CK2" s="9" t="inlineStr"/>
+      <c r="CL2" s="9" t="inlineStr"/>
+      <c r="CM2" s="9" t="inlineStr"/>
+      <c r="CN2" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CO2" s="5" t="n">
         <v>0.001</v>
       </c>
-      <c r="CP2" s="10" t="inlineStr"/>
-      <c r="CQ2" s="10" t="inlineStr"/>
-      <c r="CR2" s="10" t="inlineStr"/>
-      <c r="CS2" s="10" t="inlineStr"/>
-      <c r="CT2" s="9" t="inlineStr">
+      <c r="CP2" s="9" t="inlineStr"/>
+      <c r="CQ2" s="9" t="inlineStr"/>
+      <c r="CR2" s="9" t="inlineStr"/>
+      <c r="CS2" s="9" t="inlineStr"/>
+      <c r="CT2" s="8" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>

--- a/datos/datos_calidad_aire_DIARIO.xlsx
+++ b/datos/datos_calidad_aire_DIARIO.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="I3" s="9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="S3" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T3" s="10" t="inlineStr"/>
       <c r="U3" s="10" t="inlineStr"/>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="AC3" s="9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AD3" s="4" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="BQ3" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BR3" s="4" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="BU3" s="5" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="BV3" s="10" t="inlineStr"/>
       <c r="BW3" s="10" t="inlineStr"/>
@@ -1676,12 +1676,24 @@
         </is>
       </c>
       <c r="CF3" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="CG3" s="10" t="inlineStr"/>
-      <c r="CH3" s="10" t="inlineStr"/>
-      <c r="CI3" s="10" t="inlineStr"/>
-      <c r="CJ3" s="10" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="CG3" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
+        </is>
+      </c>
+      <c r="CH3" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="CI3" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
+        </is>
+      </c>
+      <c r="CJ3" s="9" t="n">
+        <v>30</v>
+      </c>
       <c r="CK3" s="10" t="inlineStr"/>
       <c r="CL3" s="10" t="inlineStr"/>
       <c r="CM3" s="7" t="inlineStr">
@@ -1700,13 +1712,13 @@
       <c r="CP3" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="CQ3" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="CQ3" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="CR3" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CS3" s="10" t="inlineStr"/>
       <c r="CT3" s="10" t="inlineStr"/>
@@ -1721,7 +1733,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -1729,7 +1741,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.039</v>
+        <v>0.048</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -1745,7 +1757,7 @@
         </is>
       </c>
       <c r="I4" s="9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -1767,7 +1779,7 @@
         </is>
       </c>
       <c r="S4" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T4" s="10" t="inlineStr"/>
       <c r="U4" s="10" t="inlineStr"/>
@@ -1777,7 +1789,7 @@
         </is>
       </c>
       <c r="W4" s="5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X4" s="4" t="inlineStr">
         <is>
@@ -1785,7 +1797,7 @@
         </is>
       </c>
       <c r="Y4" s="6" t="n">
-        <v>0.026</v>
+        <v>0.045</v>
       </c>
       <c r="Z4" s="7" t="inlineStr">
         <is>
@@ -1801,7 +1813,7 @@
         </is>
       </c>
       <c r="AC4" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD4" s="4" t="inlineStr">
         <is>
@@ -1827,7 +1839,7 @@
         </is>
       </c>
       <c r="AQ4" s="5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AR4" s="4" t="inlineStr">
         <is>
@@ -1851,7 +1863,7 @@
         </is>
       </c>
       <c r="AW4" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AX4" s="4" t="inlineStr">
         <is>
@@ -1867,7 +1879,7 @@
         </is>
       </c>
       <c r="BA4" s="5" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="BB4" s="4" t="inlineStr">
         <is>
@@ -1941,7 +1953,7 @@
         </is>
       </c>
       <c r="BU4" s="5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BV4" s="10" t="inlineStr"/>
       <c r="BW4" s="10" t="inlineStr"/>
@@ -1959,7 +1971,7 @@
         </is>
       </c>
       <c r="CA4" s="9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="CB4" s="4" t="inlineStr">
         <is>
@@ -1980,7 +1992,7 @@
         </is>
       </c>
       <c r="CF4" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CG4" s="8" t="inlineStr">
         <is>
@@ -1996,7 +2008,7 @@
         </is>
       </c>
       <c r="CJ4" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CK4" s="10" t="inlineStr"/>
       <c r="CL4" s="10" t="inlineStr"/>
@@ -2006,7 +2018,7 @@
         </is>
       </c>
       <c r="CN4" s="9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CO4" s="7" t="inlineStr">
         <is>
@@ -2045,7 +2057,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -2083,7 +2095,7 @@
         </is>
       </c>
       <c r="S5" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T5" s="10" t="inlineStr"/>
       <c r="U5" s="10" t="inlineStr"/>
@@ -2151,7 +2163,7 @@
         </is>
       </c>
       <c r="AS5" s="6" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="AT5" s="4" t="inlineStr">
         <is>
@@ -2167,7 +2179,7 @@
         </is>
       </c>
       <c r="AW5" s="9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX5" s="4" t="inlineStr">
         <is>
@@ -2310,7 +2322,7 @@
         </is>
       </c>
       <c r="CN5" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CO5" s="7" t="inlineStr">
         <is>
@@ -2381,13 +2393,13 @@
       <c r="O6" s="10" t="inlineStr"/>
       <c r="P6" s="10" t="inlineStr"/>
       <c r="Q6" s="10" t="inlineStr"/>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="S6" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="10" t="inlineStr"/>
@@ -2471,7 +2483,7 @@
         </is>
       </c>
       <c r="AW6" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AX6" s="4" t="inlineStr">
         <is>
@@ -2487,7 +2499,7 @@
         </is>
       </c>
       <c r="BA6" s="5" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="BB6" s="4" t="inlineStr">
         <is>
@@ -2511,7 +2523,7 @@
         </is>
       </c>
       <c r="BG6" s="9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BH6" s="10" t="inlineStr"/>
       <c r="BI6" s="10" t="inlineStr"/>
@@ -2579,7 +2591,7 @@
         </is>
       </c>
       <c r="CA6" s="9" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="CB6" s="4" t="inlineStr">
         <is>
@@ -2600,10 +2612,16 @@
         </is>
       </c>
       <c r="CF6" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="CG6" s="10" t="inlineStr"/>
-      <c r="CH6" s="10" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="CG6" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
+        </is>
+      </c>
+      <c r="CH6" s="5" t="n">
+        <v>44</v>
+      </c>
       <c r="CI6" s="8" t="inlineStr">
         <is>
           <t>Mala</t>
@@ -2651,7 +2669,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -2675,7 +2693,7 @@
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -2691,13 +2709,13 @@
       <c r="O7" s="10" t="inlineStr"/>
       <c r="P7" s="10" t="inlineStr"/>
       <c r="Q7" s="10" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="S7" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T7" s="10" t="inlineStr"/>
       <c r="U7" s="10" t="inlineStr"/>
@@ -2707,7 +2725,7 @@
         </is>
       </c>
       <c r="W7" s="5" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
@@ -2715,7 +2733,7 @@
         </is>
       </c>
       <c r="Y7" s="6" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="Z7" s="8" t="inlineStr">
         <is>
@@ -2725,13 +2743,13 @@
       <c r="AA7" s="6" t="n">
         <v>0.101</v>
       </c>
-      <c r="AB7" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="AB7" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="AC7" s="9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
@@ -2757,7 +2775,7 @@
         </is>
       </c>
       <c r="AQ7" s="5" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AR7" s="7" t="inlineStr">
         <is>
@@ -2781,7 +2799,7 @@
         </is>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AX7" s="4" t="inlineStr">
         <is>
@@ -2797,7 +2815,7 @@
         </is>
       </c>
       <c r="BA7" s="5" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="BB7" s="4" t="inlineStr">
         <is>
@@ -2821,7 +2839,7 @@
         </is>
       </c>
       <c r="BG7" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BH7" s="10" t="inlineStr"/>
       <c r="BI7" s="10" t="inlineStr"/>
@@ -2871,7 +2889,7 @@
         </is>
       </c>
       <c r="BU7" s="5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BV7" s="10" t="inlineStr"/>
       <c r="BW7" s="10" t="inlineStr"/>
@@ -2889,7 +2907,7 @@
         </is>
       </c>
       <c r="CA7" s="9" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="CB7" s="4" t="inlineStr">
         <is>
@@ -2920,7 +2938,7 @@
         </is>
       </c>
       <c r="CJ7" s="9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CK7" s="10" t="inlineStr"/>
       <c r="CL7" s="10" t="inlineStr"/>
@@ -2985,7 +3003,7 @@
         </is>
       </c>
       <c r="I8" s="9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -3091,7 +3109,7 @@
         </is>
       </c>
       <c r="AW8" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AX8" s="4" t="inlineStr">
         <is>
@@ -3205,7 +3223,7 @@
         </is>
       </c>
       <c r="CA8" s="9" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="CB8" s="4" t="inlineStr">
         <is>
@@ -3226,7 +3244,7 @@
         </is>
       </c>
       <c r="CF8" s="9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="CG8" s="10" t="inlineStr"/>
       <c r="CH8" s="10" t="inlineStr"/>
@@ -3240,13 +3258,13 @@
       </c>
       <c r="CK8" s="10" t="inlineStr"/>
       <c r="CL8" s="10" t="inlineStr"/>
-      <c r="CM8" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="CM8" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="CN8" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CO8" s="7" t="inlineStr">
         <is>
@@ -3277,7 +3295,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -3301,7 +3319,7 @@
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -3323,7 +3341,7 @@
         </is>
       </c>
       <c r="S9" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T9" s="10" t="inlineStr"/>
       <c r="U9" s="10" t="inlineStr"/>
@@ -3333,7 +3351,7 @@
         </is>
       </c>
       <c r="W9" s="5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X9" s="7" t="inlineStr">
         <is>
@@ -3357,7 +3375,7 @@
         </is>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD9" s="4" t="inlineStr">
         <is>
@@ -3475,7 +3493,7 @@
         </is>
       </c>
       <c r="BQ9" s="9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="BR9" s="4" t="inlineStr">
         <is>
@@ -3491,7 +3509,7 @@
         </is>
       </c>
       <c r="BU9" s="5" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="BV9" s="10" t="inlineStr"/>
       <c r="BW9" s="10" t="inlineStr"/>
@@ -3509,7 +3527,7 @@
         </is>
       </c>
       <c r="CA9" s="9" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="CB9" s="4" t="inlineStr">
         <is>
@@ -3530,10 +3548,16 @@
         </is>
       </c>
       <c r="CF9" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="CG9" s="10" t="inlineStr"/>
-      <c r="CH9" s="10" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="CG9" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
+        </is>
+      </c>
+      <c r="CH9" s="5" t="n">
+        <v>53</v>
+      </c>
       <c r="CI9" s="8" t="inlineStr">
         <is>
           <t>Mala</t>
@@ -3550,7 +3574,7 @@
         </is>
       </c>
       <c r="CN9" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CO9" s="8" t="inlineStr">
         <is>
@@ -3566,7 +3590,7 @@
         </is>
       </c>
       <c r="CR9" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CS9" s="10" t="inlineStr"/>
       <c r="CT9" s="10" t="inlineStr"/>
@@ -3581,7 +3605,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -3605,7 +3629,7 @@
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -3627,7 +3651,7 @@
         </is>
       </c>
       <c r="S10" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T10" s="10" t="inlineStr"/>
       <c r="U10" s="10" t="inlineStr"/>
@@ -3681,7 +3705,7 @@
         </is>
       </c>
       <c r="AQ10" s="5" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AR10" s="7" t="inlineStr">
         <is>
@@ -3705,7 +3729,7 @@
         </is>
       </c>
       <c r="AW10" s="9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AX10" s="4" t="inlineStr">
         <is>
@@ -3733,7 +3757,7 @@
         </is>
       </c>
       <c r="BG10" s="9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BH10" s="4" t="inlineStr">
         <is>
@@ -3749,7 +3773,7 @@
         </is>
       </c>
       <c r="BK10" s="5" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="BL10" s="4" t="inlineStr">
         <is>
@@ -3773,7 +3797,7 @@
         </is>
       </c>
       <c r="BQ10" s="9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BR10" s="4" t="inlineStr">
         <is>
@@ -3807,7 +3831,7 @@
         </is>
       </c>
       <c r="CA10" s="9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="CB10" s="4" t="inlineStr">
         <is>
@@ -3828,7 +3852,7 @@
         </is>
       </c>
       <c r="CF10" s="9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CG10" s="10" t="inlineStr"/>
       <c r="CH10" s="10" t="inlineStr"/>
@@ -3850,7 +3874,7 @@
         </is>
       </c>
       <c r="CP10" s="9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="CQ10" s="8" t="inlineStr">
         <is>
@@ -3873,7 +3897,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -3897,7 +3921,7 @@
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -3905,7 +3929,7 @@
         </is>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="L11" s="10" t="inlineStr"/>
       <c r="M11" s="10" t="inlineStr"/>
@@ -3919,7 +3943,7 @@
         </is>
       </c>
       <c r="S11" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T11" s="10" t="inlineStr"/>
       <c r="U11" s="10" t="inlineStr"/>
@@ -3929,7 +3953,7 @@
         </is>
       </c>
       <c r="W11" s="5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
@@ -3937,7 +3961,7 @@
         </is>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="Z11" s="7" t="inlineStr">
         <is>
@@ -3953,7 +3977,7 @@
         </is>
       </c>
       <c r="AC11" s="9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AD11" s="4" t="inlineStr">
         <is>
@@ -3961,7 +3985,7 @@
         </is>
       </c>
       <c r="AE11" s="6" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AF11" s="10" t="inlineStr"/>
       <c r="AG11" s="10" t="inlineStr"/>
@@ -3979,7 +4003,7 @@
         </is>
       </c>
       <c r="AQ11" s="5" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="AR11" s="4" t="inlineStr">
         <is>
@@ -4031,7 +4055,7 @@
         </is>
       </c>
       <c r="BG11" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BH11" s="4" t="inlineStr">
         <is>
@@ -4047,7 +4071,7 @@
         </is>
       </c>
       <c r="BK11" s="5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="BL11" s="4" t="inlineStr">
         <is>
@@ -4071,7 +4095,7 @@
         </is>
       </c>
       <c r="BQ11" s="9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BR11" s="4" t="inlineStr">
         <is>
@@ -4105,7 +4129,7 @@
         </is>
       </c>
       <c r="CA11" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="CB11" s="4" t="inlineStr">
         <is>
@@ -4126,7 +4150,7 @@
         </is>
       </c>
       <c r="CF11" s="9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CG11" s="10" t="inlineStr"/>
       <c r="CH11" s="10" t="inlineStr"/>
@@ -4136,7 +4160,7 @@
         </is>
       </c>
       <c r="CJ11" s="9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="CK11" s="10" t="inlineStr"/>
       <c r="CL11" s="10" t="inlineStr"/>
@@ -4162,7 +4186,7 @@
         </is>
       </c>
       <c r="CR11" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CS11" s="10" t="inlineStr"/>
       <c r="CT11" s="10" t="inlineStr"/>
@@ -4201,7 +4225,7 @@
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -4277,7 +4301,7 @@
         </is>
       </c>
       <c r="AQ12" s="5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AR12" s="4" t="inlineStr">
         <is>
@@ -4293,7 +4317,7 @@
         </is>
       </c>
       <c r="AU12" s="6" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="AV12" s="4" t="inlineStr">
         <is>
@@ -4301,7 +4325,7 @@
         </is>
       </c>
       <c r="AW12" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX12" s="4" t="inlineStr">
         <is>
@@ -4363,7 +4387,7 @@
         </is>
       </c>
       <c r="BQ12" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="BR12" s="4" t="inlineStr">
         <is>
@@ -4432,7 +4456,7 @@
         </is>
       </c>
       <c r="CN12" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CO12" s="4" t="inlineStr">
         <is>
@@ -4471,7 +4495,7 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -4537,7 +4561,7 @@
         </is>
       </c>
       <c r="AC13" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
@@ -4587,7 +4611,7 @@
         </is>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX13" s="4" t="inlineStr">
         <is>
@@ -4627,7 +4651,7 @@
         </is>
       </c>
       <c r="BG13" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH13" s="4" t="inlineStr">
         <is>
@@ -4667,7 +4691,7 @@
         </is>
       </c>
       <c r="BQ13" s="9" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BR13" s="4" t="inlineStr">
         <is>
@@ -4701,7 +4725,7 @@
         </is>
       </c>
       <c r="CA13" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="CB13" s="4" t="inlineStr">
         <is>
@@ -4716,18 +4740,24 @@
           <t>Mala</t>
         </is>
       </c>
-      <c r="CE13" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="CE13" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
         </is>
       </c>
       <c r="CF13" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CG13" s="10" t="inlineStr"/>
       <c r="CH13" s="10" t="inlineStr"/>
-      <c r="CI13" s="10" t="inlineStr"/>
-      <c r="CJ13" s="10" t="inlineStr"/>
+      <c r="CI13" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="CJ13" s="9" t="n">
+        <v>14</v>
+      </c>
       <c r="CK13" s="10" t="inlineStr"/>
       <c r="CL13" s="10" t="inlineStr"/>
       <c r="CM13" s="4" t="inlineStr">
@@ -4791,7 +4821,7 @@
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -4813,7 +4843,7 @@
         </is>
       </c>
       <c r="S14" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T14" s="10" t="inlineStr"/>
       <c r="U14" s="10" t="inlineStr"/>
@@ -4897,7 +4927,7 @@
         </is>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX14" s="4" t="inlineStr">
         <is>
@@ -4913,7 +4943,7 @@
         </is>
       </c>
       <c r="BA14" s="5" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="BB14" s="4" t="inlineStr">
         <is>
@@ -4933,8 +4963,14 @@
       </c>
       <c r="BF14" s="10" t="inlineStr"/>
       <c r="BG14" s="10" t="inlineStr"/>
-      <c r="BH14" s="10" t="inlineStr"/>
-      <c r="BI14" s="10" t="inlineStr"/>
+      <c r="BH14" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BI14" s="6" t="n">
+        <v>0.001</v>
+      </c>
       <c r="BJ14" s="4" t="inlineStr">
         <is>
           <t>Buena</t>
@@ -4965,7 +5001,7 @@
         </is>
       </c>
       <c r="BQ14" s="9" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="BR14" s="4" t="inlineStr">
         <is>
@@ -5014,13 +5050,13 @@
           <t>Mala</t>
         </is>
       </c>
-      <c r="CE14" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="CE14" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
         </is>
       </c>
       <c r="CF14" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CG14" s="10" t="inlineStr"/>
       <c r="CH14" s="10" t="inlineStr"/>
@@ -5139,7 +5175,7 @@
         </is>
       </c>
       <c r="AC15" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
@@ -5165,7 +5201,7 @@
         </is>
       </c>
       <c r="AQ15" s="5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AR15" s="4" t="inlineStr">
         <is>
@@ -5173,7 +5209,7 @@
         </is>
       </c>
       <c r="AS15" s="6" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="AT15" s="4" t="inlineStr">
         <is>
@@ -5189,7 +5225,7 @@
         </is>
       </c>
       <c r="AW15" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AX15" s="4" t="inlineStr">
         <is>
@@ -5297,7 +5333,7 @@
         </is>
       </c>
       <c r="CA15" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="CB15" s="4" t="inlineStr">
         <is>
@@ -5357,7 +5393,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -5413,7 +5449,7 @@
         </is>
       </c>
       <c r="W16" s="5" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X16" s="4" t="inlineStr">
         <is>
@@ -5437,7 +5473,7 @@
         </is>
       </c>
       <c r="AC16" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
@@ -5487,7 +5523,7 @@
         </is>
       </c>
       <c r="AW16" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX16" s="4" t="inlineStr">
         <is>
@@ -5521,8 +5557,14 @@
       <c r="BE16" s="6" t="n">
         <v>0.051</v>
       </c>
-      <c r="BF16" s="10" t="inlineStr"/>
-      <c r="BG16" s="10" t="inlineStr"/>
+      <c r="BF16" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="BG16" s="9" t="n">
+        <v>29</v>
+      </c>
       <c r="BH16" s="4" t="inlineStr">
         <is>
           <t>Buena</t>
@@ -5537,7 +5579,7 @@
         </is>
       </c>
       <c r="BK16" s="5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BL16" s="4" t="inlineStr">
         <is>
@@ -5545,7 +5587,7 @@
         </is>
       </c>
       <c r="BM16" s="6" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="BN16" s="4" t="inlineStr">
         <is>
@@ -5561,7 +5603,7 @@
         </is>
       </c>
       <c r="BQ16" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BR16" s="4" t="inlineStr">
         <is>
@@ -5595,7 +5637,7 @@
         </is>
       </c>
       <c r="CA16" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="CB16" s="4" t="inlineStr">
         <is>
@@ -5610,8 +5652,14 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="CE16" s="10" t="inlineStr"/>
-      <c r="CF16" s="10" t="inlineStr"/>
+      <c r="CE16" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="CF16" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="CG16" s="10" t="inlineStr"/>
       <c r="CH16" s="10" t="inlineStr"/>
       <c r="CI16" s="10" t="inlineStr"/>
@@ -5640,7 +5688,7 @@
         </is>
       </c>
       <c r="CR16" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CS16" s="10" t="inlineStr"/>
       <c r="CT16" s="10" t="inlineStr"/>
@@ -5679,7 +5727,7 @@
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -5695,13 +5743,13 @@
       <c r="O17" s="10" t="inlineStr"/>
       <c r="P17" s="10" t="inlineStr"/>
       <c r="Q17" s="10" t="inlineStr"/>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="S17" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T17" s="10" t="inlineStr"/>
       <c r="U17" s="10" t="inlineStr"/>
@@ -5735,7 +5783,7 @@
         </is>
       </c>
       <c r="AC17" s="9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
@@ -5777,7 +5825,7 @@
         </is>
       </c>
       <c r="AU17" s="6" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="AV17" s="8" t="inlineStr">
         <is>
@@ -5785,7 +5833,7 @@
         </is>
       </c>
       <c r="AW17" s="9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AX17" s="4" t="inlineStr">
         <is>
@@ -5865,7 +5913,7 @@
         </is>
       </c>
       <c r="BQ17" s="9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="BR17" s="4" t="inlineStr">
         <is>
@@ -5881,7 +5929,7 @@
         </is>
       </c>
       <c r="BU17" s="5" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="BV17" s="10" t="inlineStr"/>
       <c r="BW17" s="10" t="inlineStr"/>
@@ -5899,7 +5947,7 @@
         </is>
       </c>
       <c r="CA17" s="9" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="CB17" s="4" t="inlineStr">
         <is>
@@ -5920,7 +5968,7 @@
         </is>
       </c>
       <c r="CF17" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CG17" s="10" t="inlineStr"/>
       <c r="CH17" s="10" t="inlineStr"/>
@@ -5930,7 +5978,7 @@
         </is>
       </c>
       <c r="CJ17" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CK17" s="10" t="inlineStr"/>
       <c r="CL17" s="10" t="inlineStr"/>
@@ -5989,13 +6037,13 @@
       <c r="G18" s="6" t="n">
         <v>0.061</v>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -6017,7 +6065,7 @@
         </is>
       </c>
       <c r="S18" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T18" s="10" t="inlineStr"/>
       <c r="U18" s="10" t="inlineStr"/>
@@ -6027,7 +6075,7 @@
         </is>
       </c>
       <c r="W18" s="5" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="X18" s="4" t="inlineStr">
         <is>
@@ -6051,7 +6099,7 @@
         </is>
       </c>
       <c r="AC18" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
@@ -6077,15 +6125,15 @@
         </is>
       </c>
       <c r="AQ18" s="5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AR18" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+        <v>2.17</v>
+      </c>
+      <c r="AR18" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="AS18" s="6" t="n">
-        <v>0.041</v>
+        <v>0.057</v>
       </c>
       <c r="AT18" s="4" t="inlineStr">
         <is>
@@ -6101,7 +6149,7 @@
         </is>
       </c>
       <c r="AW18" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AX18" s="4" t="inlineStr">
         <is>
@@ -6151,7 +6199,7 @@
         </is>
       </c>
       <c r="BK18" s="5" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="BL18" s="4" t="inlineStr">
         <is>
@@ -6175,7 +6223,7 @@
         </is>
       </c>
       <c r="BQ18" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="BR18" s="4" t="inlineStr">
         <is>
@@ -6191,7 +6239,7 @@
         </is>
       </c>
       <c r="BU18" s="5" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="BV18" s="10" t="inlineStr"/>
       <c r="BW18" s="10" t="inlineStr"/>
@@ -6230,7 +6278,7 @@
         </is>
       </c>
       <c r="CF18" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CG18" s="4" t="inlineStr">
         <is>
@@ -6246,7 +6294,7 @@
         </is>
       </c>
       <c r="CJ18" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CK18" s="10" t="inlineStr"/>
       <c r="CL18" s="10" t="inlineStr"/>
@@ -6256,7 +6304,7 @@
         </is>
       </c>
       <c r="CN18" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CO18" s="8" t="inlineStr">
         <is>
@@ -6287,7 +6335,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
@@ -6295,7 +6343,7 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -6311,7 +6359,7 @@
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -6319,7 +6367,7 @@
         </is>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="L19" s="10" t="inlineStr"/>
       <c r="M19" s="10" t="inlineStr"/>
@@ -6333,7 +6381,7 @@
         </is>
       </c>
       <c r="S19" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T19" s="10" t="inlineStr"/>
       <c r="U19" s="10" t="inlineStr"/>
@@ -6351,7 +6399,7 @@
         </is>
       </c>
       <c r="Y19" s="6" t="n">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
       <c r="Z19" s="4" t="inlineStr">
         <is>
@@ -6367,7 +6415,7 @@
         </is>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AD19" s="4" t="inlineStr">
         <is>
@@ -6393,7 +6441,7 @@
         </is>
       </c>
       <c r="AQ19" s="5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AR19" s="4" t="inlineStr">
         <is>
@@ -6473,7 +6521,7 @@
         </is>
       </c>
       <c r="BK19" s="5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BL19" s="4" t="inlineStr">
         <is>
@@ -6481,7 +6529,7 @@
         </is>
       </c>
       <c r="BM19" s="6" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="BN19" s="4" t="inlineStr">
         <is>
@@ -6497,7 +6545,7 @@
         </is>
       </c>
       <c r="BQ19" s="9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BR19" s="4" t="inlineStr">
         <is>
@@ -6513,7 +6561,7 @@
         </is>
       </c>
       <c r="BU19" s="5" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="BV19" s="10" t="inlineStr"/>
       <c r="BW19" s="10" t="inlineStr"/>
@@ -6531,7 +6579,7 @@
         </is>
       </c>
       <c r="CA19" s="9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CB19" s="4" t="inlineStr">
         <is>
@@ -6552,7 +6600,7 @@
         </is>
       </c>
       <c r="CF19" s="9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CG19" s="4" t="inlineStr">
         <is>
@@ -6568,7 +6616,7 @@
         </is>
       </c>
       <c r="CJ19" s="9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CK19" s="10" t="inlineStr"/>
       <c r="CL19" s="10" t="inlineStr"/>
@@ -6594,7 +6642,7 @@
         </is>
       </c>
       <c r="CR19" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CS19" s="10" t="inlineStr"/>
       <c r="CT19" s="10" t="inlineStr"/>
@@ -6633,7 +6681,7 @@
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -6649,8 +6697,14 @@
       <c r="O20" s="10" t="inlineStr"/>
       <c r="P20" s="10" t="inlineStr"/>
       <c r="Q20" s="10" t="inlineStr"/>
-      <c r="R20" s="10" t="inlineStr"/>
-      <c r="S20" s="10" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>39</v>
+      </c>
       <c r="T20" s="10" t="inlineStr"/>
       <c r="U20" s="10" t="inlineStr"/>
       <c r="V20" s="4" t="inlineStr">
@@ -6683,7 +6737,7 @@
         </is>
       </c>
       <c r="AC20" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
@@ -6773,7 +6827,7 @@
         </is>
       </c>
       <c r="BG20" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="BH20" s="4" t="inlineStr">
         <is>
@@ -6847,7 +6901,7 @@
         </is>
       </c>
       <c r="CA20" s="9" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="CB20" s="4" t="inlineStr">
         <is>
@@ -6878,8 +6932,14 @@
       <c r="CH20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CI20" s="10" t="inlineStr"/>
-      <c r="CJ20" s="10" t="inlineStr"/>
+      <c r="CI20" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="CJ20" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="CK20" s="10" t="inlineStr"/>
       <c r="CL20" s="10" t="inlineStr"/>
       <c r="CM20" s="4" t="inlineStr">
@@ -6896,7 +6956,7 @@
         </is>
       </c>
       <c r="CP20" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CQ20" s="4" t="inlineStr">
         <is>
@@ -6904,7 +6964,7 @@
         </is>
       </c>
       <c r="CR20" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CS20" s="10" t="inlineStr"/>
       <c r="CT20" s="10" t="inlineStr"/>
@@ -6943,7 +7003,7 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -6993,13 +7053,13 @@
       <c r="AA21" s="6" t="n">
         <v>0.056</v>
       </c>
-      <c r="AB21" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="AB21" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="AC21" s="9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD21" s="4" t="inlineStr">
         <is>
@@ -7025,7 +7085,7 @@
         </is>
       </c>
       <c r="AQ21" s="5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AR21" s="4" t="inlineStr">
         <is>
@@ -7065,7 +7125,7 @@
         </is>
       </c>
       <c r="BA21" s="5" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BB21" s="4" t="inlineStr">
         <is>
@@ -7089,7 +7149,7 @@
         </is>
       </c>
       <c r="BG21" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH21" s="4" t="inlineStr">
         <is>
@@ -7129,7 +7189,7 @@
         </is>
       </c>
       <c r="BQ21" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BR21" s="4" t="inlineStr">
         <is>
@@ -7145,7 +7205,7 @@
         </is>
       </c>
       <c r="BU21" s="5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BV21" s="10" t="inlineStr"/>
       <c r="BW21" s="10" t="inlineStr"/>
@@ -7163,7 +7223,7 @@
         </is>
       </c>
       <c r="CA21" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="CB21" s="4" t="inlineStr">
         <is>
@@ -7200,7 +7260,7 @@
         </is>
       </c>
       <c r="CJ21" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CK21" s="10" t="inlineStr"/>
       <c r="CL21" s="10" t="inlineStr"/>
@@ -7321,7 +7381,7 @@
         </is>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
@@ -7371,7 +7431,7 @@
         </is>
       </c>
       <c r="AW22" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AX22" s="4" t="inlineStr">
         <is>
@@ -7395,7 +7455,7 @@
         </is>
       </c>
       <c r="BC22" s="6" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="BD22" s="4" t="inlineStr">
         <is>
@@ -7451,7 +7511,7 @@
         </is>
       </c>
       <c r="BQ22" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="BR22" s="4" t="inlineStr">
         <is>
@@ -7485,7 +7545,7 @@
         </is>
       </c>
       <c r="CA22" s="9" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="CB22" s="4" t="inlineStr">
         <is>
@@ -7522,7 +7582,7 @@
         </is>
       </c>
       <c r="CJ22" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CK22" s="10" t="inlineStr"/>
       <c r="CL22" s="10" t="inlineStr"/>
@@ -7663,7 +7723,7 @@
         </is>
       </c>
       <c r="AQ23" s="5" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AR23" s="7" t="inlineStr">
         <is>
@@ -7795,7 +7855,7 @@
         </is>
       </c>
       <c r="CA23" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="CB23" s="4" t="inlineStr">
         <is>
@@ -7861,7 +7921,7 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
@@ -7869,7 +7929,7 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.031</v>
+        <v>0.034</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -7885,7 +7945,7 @@
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -7907,7 +7967,7 @@
         </is>
       </c>
       <c r="S24" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T24" s="10" t="inlineStr"/>
       <c r="U24" s="10" t="inlineStr"/>
@@ -7925,7 +7985,7 @@
         </is>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
       <c r="Z24" s="4" t="inlineStr">
         <is>
@@ -8075,7 +8135,7 @@
         </is>
       </c>
       <c r="BU24" s="5" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BV24" s="10" t="inlineStr"/>
       <c r="BW24" s="10" t="inlineStr"/>
@@ -8114,7 +8174,7 @@
         </is>
       </c>
       <c r="CF24" s="9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CG24" s="4" t="inlineStr">
         <is>
@@ -8134,7 +8194,7 @@
         </is>
       </c>
       <c r="CN24" s="9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CO24" s="4" t="inlineStr">
         <is>
@@ -8249,7 +8309,7 @@
         </is>
       </c>
       <c r="AS25" s="6" t="n">
-        <v>0.043</v>
+        <v>0.048</v>
       </c>
       <c r="AT25" s="4" t="inlineStr">
         <is>
@@ -8265,7 +8325,7 @@
         </is>
       </c>
       <c r="AW25" s="9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AX25" s="4" t="inlineStr">
         <is>
@@ -8339,7 +8399,7 @@
         </is>
       </c>
       <c r="BQ25" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BR25" s="4" t="inlineStr">
         <is>
@@ -8355,7 +8415,7 @@
         </is>
       </c>
       <c r="BU25" s="5" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BV25" s="10" t="inlineStr"/>
       <c r="BW25" s="10" t="inlineStr"/>
@@ -8373,7 +8433,7 @@
         </is>
       </c>
       <c r="CA25" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="CB25" s="4" t="inlineStr">
         <is>
@@ -8491,7 +8551,7 @@
         </is>
       </c>
       <c r="S26" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T26" s="10" t="inlineStr"/>
       <c r="U26" s="10" t="inlineStr"/>
@@ -8545,7 +8605,7 @@
         </is>
       </c>
       <c r="AW26" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AX26" s="4" t="inlineStr">
         <is>
@@ -8595,7 +8655,7 @@
         </is>
       </c>
       <c r="BK26" s="5" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="BL26" s="4" t="inlineStr">
         <is>
@@ -8619,7 +8679,7 @@
         </is>
       </c>
       <c r="BQ26" s="9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BR26" s="4" t="inlineStr">
         <is>
@@ -8635,7 +8695,7 @@
         </is>
       </c>
       <c r="BU26" s="5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BV26" s="10" t="inlineStr"/>
       <c r="BW26" s="10" t="inlineStr"/>
@@ -8653,7 +8713,7 @@
         </is>
       </c>
       <c r="CA26" s="9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="CB26" s="4" t="inlineStr">
         <is>
@@ -8702,7 +8762,7 @@
         </is>
       </c>
       <c r="CP26" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CQ26" s="4" t="inlineStr">
         <is>
@@ -8710,7 +8770,7 @@
         </is>
       </c>
       <c r="CR26" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CS26" s="10" t="inlineStr"/>
       <c r="CT26" s="10" t="inlineStr"/>
@@ -8771,7 +8831,7 @@
         </is>
       </c>
       <c r="S27" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T27" s="10" t="inlineStr"/>
       <c r="U27" s="10" t="inlineStr"/>
@@ -8825,7 +8885,7 @@
         </is>
       </c>
       <c r="AQ27" s="5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AR27" s="4" t="inlineStr">
         <is>
@@ -8833,7 +8893,7 @@
         </is>
       </c>
       <c r="AS27" s="6" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="AT27" s="4" t="inlineStr">
         <is>
@@ -8899,7 +8959,7 @@
         </is>
       </c>
       <c r="BK27" s="5" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BL27" s="4" t="inlineStr">
         <is>
@@ -8957,7 +9017,7 @@
         </is>
       </c>
       <c r="CA27" s="9" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="CB27" s="4" t="inlineStr">
         <is>
@@ -9193,7 +9253,7 @@
         </is>
       </c>
       <c r="BG28" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH28" s="4" t="inlineStr">
         <is>
@@ -9357,7 +9417,7 @@
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -9379,7 +9439,7 @@
         </is>
       </c>
       <c r="S29" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T29" s="10" t="inlineStr"/>
       <c r="U29" s="10" t="inlineStr"/>
@@ -9413,7 +9473,7 @@
         </is>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD29" s="4" t="inlineStr">
         <is>
@@ -9463,7 +9523,7 @@
         </is>
       </c>
       <c r="AW29" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AX29" s="4" t="inlineStr">
         <is>
@@ -9479,7 +9539,7 @@
         </is>
       </c>
       <c r="BA29" s="5" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BB29" s="4" t="inlineStr">
         <is>
@@ -9537,7 +9597,7 @@
         </is>
       </c>
       <c r="BQ29" s="9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="BR29" s="4" t="inlineStr">
         <is>
@@ -9553,7 +9613,7 @@
         </is>
       </c>
       <c r="BU29" s="5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BV29" s="10" t="inlineStr"/>
       <c r="BW29" s="10" t="inlineStr"/>
@@ -9571,7 +9631,7 @@
         </is>
       </c>
       <c r="CA29" s="9" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="CB29" s="4" t="inlineStr">
         <is>
@@ -9634,7 +9694,7 @@
         </is>
       </c>
       <c r="CR29" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CS29" s="10" t="inlineStr"/>
       <c r="CT29" s="10" t="inlineStr"/>
@@ -9673,7 +9733,7 @@
         </is>
       </c>
       <c r="I30" s="9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -9729,7 +9789,7 @@
         </is>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AD30" s="4" t="inlineStr">
         <is>
@@ -9779,7 +9839,7 @@
         </is>
       </c>
       <c r="AW30" s="9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AX30" s="4" t="inlineStr">
         <is>
@@ -9819,7 +9879,7 @@
         </is>
       </c>
       <c r="BG30" s="9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BH30" s="10" t="inlineStr"/>
       <c r="BI30" s="10" t="inlineStr"/>
@@ -9853,7 +9913,7 @@
         </is>
       </c>
       <c r="BQ30" s="9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="BR30" s="4" t="inlineStr">
         <is>
@@ -9887,7 +9947,7 @@
         </is>
       </c>
       <c r="CA30" s="9" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="CB30" s="4" t="inlineStr">
         <is>
@@ -9934,7 +9994,7 @@
         </is>
       </c>
       <c r="CN30" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CO30" s="8" t="inlineStr">
         <is>
@@ -9965,7 +10025,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
@@ -9973,7 +10033,7 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.047</v>
+        <v>0.052</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
@@ -9989,7 +10049,7 @@
         </is>
       </c>
       <c r="I31" s="9" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -10021,7 +10081,7 @@
         </is>
       </c>
       <c r="W31" s="5" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X31" s="4" t="inlineStr">
         <is>
@@ -10045,7 +10105,7 @@
         </is>
       </c>
       <c r="AC31" s="9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AD31" s="4" t="inlineStr">
         <is>
@@ -10071,7 +10131,7 @@
         </is>
       </c>
       <c r="AQ31" s="5" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AR31" s="4" t="inlineStr">
         <is>
@@ -10079,7 +10139,7 @@
         </is>
       </c>
       <c r="AS31" s="6" t="n">
-        <v>0.037</v>
+        <v>0.049</v>
       </c>
       <c r="AT31" s="4" t="inlineStr">
         <is>
@@ -10095,7 +10155,7 @@
         </is>
       </c>
       <c r="AW31" s="9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX31" s="4" t="inlineStr">
         <is>
@@ -10185,7 +10245,7 @@
         </is>
       </c>
       <c r="BU31" s="5" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BV31" s="10" t="inlineStr"/>
       <c r="BW31" s="10" t="inlineStr"/>
@@ -10203,7 +10263,7 @@
         </is>
       </c>
       <c r="CA31" s="9" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="CB31" s="4" t="inlineStr">
         <is>
@@ -10224,7 +10284,7 @@
         </is>
       </c>
       <c r="CF31" s="9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CG31" s="4" t="inlineStr">
         <is>
@@ -10240,7 +10300,7 @@
         </is>
       </c>
       <c r="CJ31" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CK31" s="10" t="inlineStr"/>
       <c r="CL31" s="10" t="inlineStr"/>
@@ -10250,7 +10310,7 @@
         </is>
       </c>
       <c r="CN31" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CO31" s="8" t="inlineStr">
         <is>
@@ -10281,7 +10341,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
@@ -10327,7 +10387,7 @@
         </is>
       </c>
       <c r="S32" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T32" s="10" t="inlineStr"/>
       <c r="U32" s="10" t="inlineStr"/>
@@ -10387,7 +10447,7 @@
         </is>
       </c>
       <c r="AQ32" s="5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AR32" s="4" t="inlineStr">
         <is>
@@ -10411,7 +10471,7 @@
         </is>
       </c>
       <c r="AW32" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX32" s="4" t="inlineStr">
         <is>
@@ -10451,7 +10511,7 @@
         </is>
       </c>
       <c r="BG32" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BH32" s="10" t="inlineStr"/>
       <c r="BI32" s="10" t="inlineStr"/>
@@ -10461,7 +10521,7 @@
         </is>
       </c>
       <c r="BK32" s="5" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BL32" s="4" t="inlineStr">
         <is>
@@ -10501,7 +10561,7 @@
         </is>
       </c>
       <c r="BU32" s="5" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BV32" s="10" t="inlineStr"/>
       <c r="BW32" s="10" t="inlineStr"/>
@@ -10519,7 +10579,7 @@
         </is>
       </c>
       <c r="CA32" s="9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="CB32" s="4" t="inlineStr">
         <is>
@@ -10621,7 +10681,7 @@
         </is>
       </c>
       <c r="I33" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -10643,7 +10703,7 @@
         </is>
       </c>
       <c r="S33" s="5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T33" s="10" t="inlineStr"/>
       <c r="U33" s="10" t="inlineStr"/>
@@ -10703,7 +10763,7 @@
         </is>
       </c>
       <c r="AQ33" s="5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AR33" s="4" t="inlineStr">
         <is>
@@ -10767,7 +10827,7 @@
         </is>
       </c>
       <c r="BG33" s="9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BH33" s="10" t="inlineStr"/>
       <c r="BI33" s="10" t="inlineStr"/>
@@ -10817,7 +10877,7 @@
         </is>
       </c>
       <c r="BU33" s="5" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="BV33" s="10" t="inlineStr"/>
       <c r="BW33" s="10" t="inlineStr"/>
@@ -10835,7 +10895,7 @@
         </is>
       </c>
       <c r="CA33" s="9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CB33" s="4" t="inlineStr">
         <is>
@@ -10856,7 +10916,7 @@
         </is>
       </c>
       <c r="CF33" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CG33" s="4" t="inlineStr">
         <is>
@@ -10953,8 +11013,14 @@
       <c r="O34" s="10" t="inlineStr"/>
       <c r="P34" s="10" t="inlineStr"/>
       <c r="Q34" s="10" t="inlineStr"/>
-      <c r="R34" s="10" t="inlineStr"/>
-      <c r="S34" s="10" t="inlineStr"/>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>44</v>
+      </c>
       <c r="T34" s="10" t="inlineStr"/>
       <c r="U34" s="10" t="inlineStr"/>
       <c r="V34" s="4" t="inlineStr">
@@ -10987,7 +11053,7 @@
         </is>
       </c>
       <c r="AC34" s="9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AD34" s="4" t="inlineStr">
         <is>
@@ -11111,7 +11177,7 @@
         </is>
       </c>
       <c r="BQ34" s="9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="BR34" s="4" t="inlineStr">
         <is>
@@ -11145,7 +11211,7 @@
         </is>
       </c>
       <c r="CA34" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="CB34" s="4" t="inlineStr">
         <is>
@@ -11247,7 +11313,7 @@
         </is>
       </c>
       <c r="I35" s="9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -11329,7 +11395,7 @@
         </is>
       </c>
       <c r="AQ35" s="5" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="AR35" s="7" t="inlineStr">
         <is>
@@ -11369,7 +11435,7 @@
         </is>
       </c>
       <c r="BA35" s="5" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BB35" s="4" t="inlineStr">
         <is>
@@ -11393,7 +11459,7 @@
         </is>
       </c>
       <c r="BG35" s="9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BH35" s="10" t="inlineStr"/>
       <c r="BI35" s="10" t="inlineStr"/>
@@ -11427,7 +11493,7 @@
         </is>
       </c>
       <c r="BQ35" s="9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="BR35" s="4" t="inlineStr">
         <is>
@@ -11482,7 +11548,7 @@
         </is>
       </c>
       <c r="CF35" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CG35" s="4" t="inlineStr">
         <is>
@@ -11508,7 +11574,7 @@
         </is>
       </c>
       <c r="CN35" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CO35" s="7" t="inlineStr">
         <is>
@@ -11516,7 +11582,7 @@
         </is>
       </c>
       <c r="CP35" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CQ35" s="7" t="inlineStr">
         <is>
@@ -11563,7 +11629,7 @@
         </is>
       </c>
       <c r="I36" s="9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -11585,7 +11651,7 @@
         </is>
       </c>
       <c r="S36" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T36" s="10" t="inlineStr"/>
       <c r="U36" s="10" t="inlineStr"/>
@@ -11639,15 +11705,15 @@
         </is>
       </c>
       <c r="AQ36" s="5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AR36" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+        <v>2.7</v>
+      </c>
+      <c r="AR36" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="AS36" s="6" t="n">
-        <v>0.047</v>
+        <v>0.059</v>
       </c>
       <c r="AT36" s="4" t="inlineStr">
         <is>
@@ -11663,7 +11729,7 @@
         </is>
       </c>
       <c r="AW36" s="9" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AX36" s="4" t="inlineStr">
         <is>
@@ -11703,7 +11769,7 @@
         </is>
       </c>
       <c r="BG36" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BH36" s="10" t="inlineStr"/>
       <c r="BI36" s="10" t="inlineStr"/>
@@ -11737,7 +11803,7 @@
         </is>
       </c>
       <c r="BQ36" s="9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="BR36" s="4" t="inlineStr">
         <is>
@@ -11753,7 +11819,7 @@
         </is>
       </c>
       <c r="BU36" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="BV36" s="4" t="inlineStr">
         <is>
@@ -11792,13 +11858,13 @@
           <t>Mala</t>
         </is>
       </c>
-      <c r="CE36" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="CE36" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="CF36" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CG36" s="4" t="inlineStr">
         <is>
@@ -11818,7 +11884,7 @@
         </is>
       </c>
       <c r="CN36" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CO36" s="7" t="inlineStr">
         <is>
@@ -11889,8 +11955,14 @@
       <c r="O37" s="10" t="inlineStr"/>
       <c r="P37" s="10" t="inlineStr"/>
       <c r="Q37" s="10" t="inlineStr"/>
-      <c r="R37" s="10" t="inlineStr"/>
-      <c r="S37" s="10" t="inlineStr"/>
+      <c r="R37" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>46</v>
+      </c>
       <c r="T37" s="10" t="inlineStr"/>
       <c r="U37" s="10" t="inlineStr"/>
       <c r="V37" s="4" t="inlineStr">
@@ -12007,7 +12079,7 @@
         </is>
       </c>
       <c r="BG37" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="BH37" s="10" t="inlineStr"/>
       <c r="BI37" s="10" t="inlineStr"/>
@@ -12017,7 +12089,7 @@
         </is>
       </c>
       <c r="BK37" s="5" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="BL37" s="4" t="inlineStr">
         <is>
@@ -12081,7 +12153,7 @@
         </is>
       </c>
       <c r="CA37" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CB37" s="4" t="inlineStr">
         <is>
@@ -12112,7 +12184,7 @@
         </is>
       </c>
       <c r="CJ37" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CK37" s="10" t="inlineStr"/>
       <c r="CL37" s="10" t="inlineStr"/>
@@ -12124,13 +12196,13 @@
       <c r="CN37" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="CO37" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="CO37" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
         </is>
       </c>
       <c r="CP37" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CQ37" s="4" t="inlineStr">
         <is>
@@ -12138,7 +12210,7 @@
         </is>
       </c>
       <c r="CR37" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CS37" s="10" t="inlineStr"/>
       <c r="CT37" s="10" t="inlineStr"/>
@@ -12199,7 +12271,7 @@
         </is>
       </c>
       <c r="S38" s="5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T38" s="10" t="inlineStr"/>
       <c r="U38" s="10" t="inlineStr"/>
@@ -12283,7 +12355,7 @@
         </is>
       </c>
       <c r="AW38" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX38" s="4" t="inlineStr">
         <is>
@@ -12418,7 +12490,7 @@
         </is>
       </c>
       <c r="CF38" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CG38" s="4" t="inlineStr">
         <is>
@@ -12434,7 +12506,7 @@
         </is>
       </c>
       <c r="CJ38" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CK38" s="10" t="inlineStr"/>
       <c r="CL38" s="10" t="inlineStr"/>
@@ -12452,7 +12524,7 @@
         </is>
       </c>
       <c r="CP38" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="CQ38" s="10" t="inlineStr"/>
       <c r="CR38" s="10" t="inlineStr"/>
@@ -12493,7 +12565,7 @@
         </is>
       </c>
       <c r="I39" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -12509,13 +12581,13 @@
       <c r="O39" s="10" t="inlineStr"/>
       <c r="P39" s="10" t="inlineStr"/>
       <c r="Q39" s="10" t="inlineStr"/>
-      <c r="R39" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="R39" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="S39" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T39" s="10" t="inlineStr"/>
       <c r="U39" s="10" t="inlineStr"/>
@@ -12599,7 +12671,7 @@
         </is>
       </c>
       <c r="AW39" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AX39" s="4" t="inlineStr">
         <is>
@@ -12639,7 +12711,7 @@
         </is>
       </c>
       <c r="BG39" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH39" s="10" t="inlineStr"/>
       <c r="BI39" s="10" t="inlineStr"/>
@@ -12713,7 +12785,7 @@
         </is>
       </c>
       <c r="CA39" s="9" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="CB39" s="4" t="inlineStr">
         <is>
@@ -12760,7 +12832,7 @@
         </is>
       </c>
       <c r="CN39" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CO39" s="4" t="inlineStr">
         <is>
@@ -12791,7 +12863,7 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
@@ -12799,7 +12871,7 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
@@ -12815,7 +12887,7 @@
         </is>
       </c>
       <c r="I40" s="9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -12837,7 +12909,7 @@
         </is>
       </c>
       <c r="S40" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T40" s="10" t="inlineStr"/>
       <c r="U40" s="10" t="inlineStr"/>
@@ -12847,7 +12919,7 @@
         </is>
       </c>
       <c r="W40" s="5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="X40" s="4" t="inlineStr">
         <is>
@@ -12915,13 +12987,13 @@
       <c r="AU40" s="6" t="n">
         <v>0.031</v>
       </c>
-      <c r="AV40" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="AV40" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="AW40" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AX40" s="4" t="inlineStr">
         <is>
@@ -12979,7 +13051,7 @@
         </is>
       </c>
       <c r="BM40" s="6" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="BN40" s="7" t="inlineStr">
         <is>
@@ -12989,13 +13061,13 @@
       <c r="BO40" s="6" t="n">
         <v>0.074</v>
       </c>
-      <c r="BP40" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="BP40" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="BQ40" s="9" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="BR40" s="4" t="inlineStr">
         <is>
@@ -13011,7 +13083,7 @@
         </is>
       </c>
       <c r="BU40" s="5" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BV40" s="4" t="inlineStr">
         <is>
@@ -13035,7 +13107,7 @@
         </is>
       </c>
       <c r="CA40" s="9" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="CB40" s="4" t="inlineStr">
         <is>
@@ -13072,7 +13144,7 @@
         </is>
       </c>
       <c r="CJ40" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CK40" s="10" t="inlineStr"/>
       <c r="CL40" s="10" t="inlineStr"/>
@@ -13098,7 +13170,7 @@
         </is>
       </c>
       <c r="CR40" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CS40" s="10" t="inlineStr"/>
       <c r="CT40" s="10" t="inlineStr"/>
@@ -13153,13 +13225,13 @@
       <c r="O41" s="10" t="inlineStr"/>
       <c r="P41" s="10" t="inlineStr"/>
       <c r="Q41" s="10" t="inlineStr"/>
-      <c r="R41" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="R41" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="S41" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T41" s="10" t="inlineStr"/>
       <c r="U41" s="10" t="inlineStr"/>
@@ -13237,13 +13309,13 @@
       <c r="AU41" s="6" t="n">
         <v>0.028</v>
       </c>
-      <c r="AV41" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="AV41" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="AW41" s="9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AX41" s="4" t="inlineStr">
         <is>
@@ -13283,7 +13355,7 @@
         </is>
       </c>
       <c r="BG41" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="BH41" s="10" t="inlineStr"/>
       <c r="BI41" s="10" t="inlineStr"/>
@@ -13317,7 +13389,7 @@
         </is>
       </c>
       <c r="BQ41" s="9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="BR41" s="4" t="inlineStr">
         <is>
@@ -13333,7 +13405,7 @@
         </is>
       </c>
       <c r="BU41" s="5" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="BV41" s="4" t="inlineStr">
         <is>
@@ -13357,7 +13429,7 @@
         </is>
       </c>
       <c r="CA41" s="9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="CB41" s="4" t="inlineStr">
         <is>
@@ -13388,8 +13460,14 @@
       <c r="CH41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CI41" s="10" t="inlineStr"/>
-      <c r="CJ41" s="10" t="inlineStr"/>
+      <c r="CI41" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
+        </is>
+      </c>
+      <c r="CJ41" s="9" t="n">
+        <v>29</v>
+      </c>
       <c r="CK41" s="10" t="inlineStr"/>
       <c r="CL41" s="10" t="inlineStr"/>
       <c r="CM41" s="7" t="inlineStr">
@@ -13453,7 +13531,7 @@
         </is>
       </c>
       <c r="I42" s="9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -13475,7 +13553,7 @@
         </is>
       </c>
       <c r="S42" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T42" s="10" t="inlineStr"/>
       <c r="U42" s="10" t="inlineStr"/>
@@ -13503,7 +13581,7 @@
         </is>
       </c>
       <c r="AC42" s="9" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AD42" s="4" t="inlineStr">
         <is>
@@ -13569,7 +13647,7 @@
         </is>
       </c>
       <c r="BA42" s="5" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="BB42" s="4" t="inlineStr">
         <is>
@@ -13627,7 +13705,7 @@
         </is>
       </c>
       <c r="BQ42" s="9" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="BR42" s="10" t="inlineStr"/>
       <c r="BS42" s="10" t="inlineStr"/>
@@ -13682,7 +13760,7 @@
         </is>
       </c>
       <c r="CF42" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CG42" s="4" t="inlineStr">
         <is>
@@ -13733,7 +13811,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -13741,7 +13819,7 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.041</v>
+        <v>0.05</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
@@ -13757,7 +13835,7 @@
         </is>
       </c>
       <c r="I43" s="9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -13779,7 +13857,7 @@
         </is>
       </c>
       <c r="S43" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T43" s="10" t="inlineStr"/>
       <c r="U43" s="10" t="inlineStr"/>
@@ -13789,7 +13867,7 @@
         </is>
       </c>
       <c r="W43" s="5" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="X43" s="4" t="inlineStr">
         <is>
@@ -13813,7 +13891,7 @@
         </is>
       </c>
       <c r="AC43" s="9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AD43" s="4" t="inlineStr">
         <is>
@@ -13839,7 +13917,7 @@
         </is>
       </c>
       <c r="AQ43" s="5" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="AR43" s="7" t="inlineStr">
         <is>
@@ -13847,7 +13925,7 @@
         </is>
       </c>
       <c r="AS43" s="6" t="n">
-        <v>0.058</v>
+        <v>0.066</v>
       </c>
       <c r="AT43" s="4" t="inlineStr">
         <is>
@@ -13863,7 +13941,7 @@
         </is>
       </c>
       <c r="AW43" s="9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AX43" s="4" t="inlineStr">
         <is>
@@ -13879,7 +13957,7 @@
         </is>
       </c>
       <c r="BA43" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BB43" s="4" t="inlineStr">
         <is>
@@ -13937,7 +14015,7 @@
         </is>
       </c>
       <c r="BQ43" s="9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BR43" s="4" t="inlineStr">
         <is>
@@ -13953,7 +14031,7 @@
         </is>
       </c>
       <c r="BU43" s="5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BV43" s="7" t="inlineStr">
         <is>
@@ -13961,7 +14039,7 @@
         </is>
       </c>
       <c r="BW43" s="6" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="BX43" s="7" t="inlineStr">
         <is>
@@ -13977,7 +14055,7 @@
         </is>
       </c>
       <c r="CA43" s="9" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="CB43" s="4" t="inlineStr">
         <is>
@@ -13998,7 +14076,7 @@
         </is>
       </c>
       <c r="CF43" s="9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="CG43" s="4" t="inlineStr">
         <is>
@@ -14014,7 +14092,7 @@
         </is>
       </c>
       <c r="CJ43" s="9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="CK43" s="10" t="inlineStr"/>
       <c r="CL43" s="10" t="inlineStr"/>
@@ -14024,7 +14102,7 @@
         </is>
       </c>
       <c r="CN43" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CO43" s="8" t="inlineStr">
         <is>
@@ -14101,7 +14179,7 @@
         </is>
       </c>
       <c r="S44" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T44" s="10" t="inlineStr"/>
       <c r="U44" s="10" t="inlineStr"/>
@@ -14293,7 +14371,7 @@
         </is>
       </c>
       <c r="CA44" s="9" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="CB44" s="4" t="inlineStr">
         <is>
@@ -14417,7 +14495,7 @@
         </is>
       </c>
       <c r="S45" s="5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T45" s="10" t="inlineStr"/>
       <c r="U45" s="10" t="inlineStr"/>
@@ -14451,7 +14529,7 @@
         </is>
       </c>
       <c r="AC45" s="9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AD45" s="4" t="inlineStr">
         <is>
@@ -14501,7 +14579,7 @@
         </is>
       </c>
       <c r="AW45" s="9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AX45" s="4" t="inlineStr">
         <is>
@@ -14575,7 +14653,7 @@
         </is>
       </c>
       <c r="BQ45" s="9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="BR45" s="10" t="inlineStr"/>
       <c r="BS45" s="10" t="inlineStr"/>
@@ -14585,7 +14663,7 @@
         </is>
       </c>
       <c r="BU45" s="5" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BV45" s="7" t="inlineStr">
         <is>
@@ -14609,7 +14687,7 @@
         </is>
       </c>
       <c r="CA45" s="9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CB45" s="4" t="inlineStr">
         <is>
@@ -14646,7 +14724,7 @@
         </is>
       </c>
       <c r="CJ45" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="CK45" s="10" t="inlineStr"/>
       <c r="CL45" s="10" t="inlineStr"/>
@@ -14664,7 +14742,7 @@
         </is>
       </c>
       <c r="CP45" s="9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CQ45" s="7" t="inlineStr">
         <is>
@@ -14711,7 +14789,7 @@
         </is>
       </c>
       <c r="I46" s="9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -14793,7 +14871,7 @@
         </is>
       </c>
       <c r="AQ46" s="5" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="AR46" s="8" t="inlineStr">
         <is>
@@ -14817,7 +14895,7 @@
         </is>
       </c>
       <c r="AW46" s="9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AX46" s="4" t="inlineStr">
         <is>
@@ -14857,7 +14935,7 @@
         </is>
       </c>
       <c r="BG46" s="9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BH46" s="10" t="inlineStr"/>
       <c r="BI46" s="10" t="inlineStr"/>
@@ -14901,7 +14979,7 @@
         </is>
       </c>
       <c r="BU46" s="5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BV46" s="7" t="inlineStr">
         <is>
@@ -14972,7 +15050,7 @@
         </is>
       </c>
       <c r="CN46" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CO46" s="8" t="inlineStr">
         <is>
@@ -14980,7 +15058,7 @@
         </is>
       </c>
       <c r="CP46" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CQ46" s="8" t="inlineStr">
         <is>
@@ -15003,7 +15081,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
@@ -15011,7 +15089,7 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>0.056</v>
+        <v>0.06</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -15027,7 +15105,7 @@
         </is>
       </c>
       <c r="I47" s="9" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -15049,7 +15127,7 @@
         </is>
       </c>
       <c r="S47" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T47" s="10" t="inlineStr"/>
       <c r="U47" s="10" t="inlineStr"/>
@@ -15097,7 +15175,7 @@
         </is>
       </c>
       <c r="AQ47" s="5" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="AR47" s="7" t="inlineStr">
         <is>
@@ -15105,7 +15183,7 @@
         </is>
       </c>
       <c r="AS47" s="6" t="n">
-        <v>0.055</v>
+        <v>0.078</v>
       </c>
       <c r="AT47" s="4" t="inlineStr">
         <is>
@@ -15121,7 +15199,7 @@
         </is>
       </c>
       <c r="AW47" s="9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AX47" s="4" t="inlineStr">
         <is>
@@ -15161,7 +15239,7 @@
         </is>
       </c>
       <c r="BG47" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BH47" s="10" t="inlineStr"/>
       <c r="BI47" s="10" t="inlineStr"/>
@@ -15171,7 +15249,7 @@
         </is>
       </c>
       <c r="BK47" s="5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BL47" s="4" t="inlineStr">
         <is>
@@ -15195,7 +15273,7 @@
         </is>
       </c>
       <c r="BQ47" s="9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="BR47" s="10" t="inlineStr"/>
       <c r="BS47" s="10" t="inlineStr"/>
@@ -15205,7 +15283,7 @@
         </is>
       </c>
       <c r="BU47" s="5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BV47" s="4" t="inlineStr">
         <is>
@@ -15229,7 +15307,7 @@
         </is>
       </c>
       <c r="CA47" s="9" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="CB47" s="4" t="inlineStr">
         <is>
@@ -15250,7 +15328,7 @@
         </is>
       </c>
       <c r="CF47" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CG47" s="4" t="inlineStr">
         <is>
@@ -15270,7 +15348,7 @@
         </is>
       </c>
       <c r="CN47" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CO47" s="8" t="inlineStr">
         <is>
@@ -15286,7 +15364,7 @@
         </is>
       </c>
       <c r="CR47" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CS47" s="10" t="inlineStr"/>
       <c r="CT47" s="10" t="inlineStr"/>
@@ -15325,7 +15403,7 @@
         </is>
       </c>
       <c r="I48" s="9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -15347,7 +15425,7 @@
         </is>
       </c>
       <c r="S48" s="5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T48" s="10" t="inlineStr"/>
       <c r="U48" s="10" t="inlineStr"/>
@@ -15381,7 +15459,7 @@
         </is>
       </c>
       <c r="AC48" s="9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AD48" s="4" t="inlineStr">
         <is>
@@ -15431,7 +15509,7 @@
         </is>
       </c>
       <c r="AW48" s="9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AX48" s="4" t="inlineStr">
         <is>
@@ -15533,7 +15611,7 @@
         </is>
       </c>
       <c r="CA48" s="9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="CB48" s="4" t="inlineStr">
         <is>
@@ -15554,7 +15632,7 @@
         </is>
       </c>
       <c r="CF48" s="9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CG48" s="4" t="inlineStr">
         <is>
@@ -15570,7 +15648,7 @@
         </is>
       </c>
       <c r="CJ48" s="9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="CK48" s="10" t="inlineStr"/>
       <c r="CL48" s="10" t="inlineStr"/>
@@ -15590,7 +15668,7 @@
         </is>
       </c>
       <c r="CR48" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CS48" s="10" t="inlineStr"/>
       <c r="CT48" s="10" t="inlineStr"/>
@@ -15629,7 +15707,7 @@
         </is>
       </c>
       <c r="I49" s="9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -15651,7 +15729,7 @@
         </is>
       </c>
       <c r="S49" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T49" s="10" t="inlineStr"/>
       <c r="U49" s="10" t="inlineStr"/>
@@ -15729,7 +15807,7 @@
         </is>
       </c>
       <c r="AW49" s="9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AX49" s="4" t="inlineStr">
         <is>
@@ -15803,7 +15881,7 @@
         </is>
       </c>
       <c r="BQ49" s="9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="BR49" s="4" t="inlineStr">
         <is>
@@ -15819,7 +15897,7 @@
         </is>
       </c>
       <c r="BU49" s="5" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BV49" s="7" t="inlineStr">
         <is>
@@ -15892,7 +15970,7 @@
         </is>
       </c>
       <c r="CP49" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CQ49" s="8" t="inlineStr">
         <is>
@@ -15961,7 +16039,7 @@
         </is>
       </c>
       <c r="S50" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="T50" s="10" t="inlineStr"/>
       <c r="U50" s="10" t="inlineStr"/>
@@ -16033,7 +16111,7 @@
         </is>
       </c>
       <c r="AW50" s="9" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AX50" s="4" t="inlineStr">
         <is>
@@ -16107,7 +16185,7 @@
         </is>
       </c>
       <c r="BQ50" s="9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BR50" s="4" t="inlineStr">
         <is>
@@ -16147,7 +16225,7 @@
         </is>
       </c>
       <c r="CA50" s="9" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="CB50" s="4" t="inlineStr">
         <is>
@@ -16190,7 +16268,7 @@
         </is>
       </c>
       <c r="CP50" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CQ50" s="8" t="inlineStr">
         <is>
@@ -16213,7 +16291,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
@@ -16231,8 +16309,14 @@
       <c r="G51" s="6" t="n">
         <v>0.068</v>
       </c>
-      <c r="H51" s="10" t="inlineStr"/>
-      <c r="I51" s="10" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="n">
+        <v>91</v>
+      </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>Buena</t>
@@ -16253,7 +16337,7 @@
         </is>
       </c>
       <c r="S51" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T51" s="10" t="inlineStr"/>
       <c r="U51" s="10" t="inlineStr"/>
@@ -16281,7 +16365,7 @@
         </is>
       </c>
       <c r="AC51" s="9" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AD51" s="10" t="inlineStr"/>
       <c r="AE51" s="10" t="inlineStr"/>
@@ -16301,7 +16385,7 @@
         </is>
       </c>
       <c r="AQ51" s="5" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="AR51" s="4" t="inlineStr">
         <is>
@@ -16309,7 +16393,7 @@
         </is>
       </c>
       <c r="AS51" s="6" t="n">
-        <v>0.042</v>
+        <v>0.046</v>
       </c>
       <c r="AT51" s="4" t="inlineStr">
         <is>
@@ -16325,7 +16409,7 @@
         </is>
       </c>
       <c r="AW51" s="9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AX51" s="4" t="inlineStr">
         <is>
@@ -16365,7 +16449,7 @@
         </is>
       </c>
       <c r="BG51" s="9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="BH51" s="10" t="inlineStr"/>
       <c r="BI51" s="10" t="inlineStr"/>
@@ -16399,7 +16483,7 @@
         </is>
       </c>
       <c r="BQ51" s="9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BR51" s="4" t="inlineStr">
         <is>
@@ -16415,7 +16499,7 @@
         </is>
       </c>
       <c r="BU51" s="5" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="BV51" s="7" t="inlineStr">
         <is>
@@ -16439,7 +16523,7 @@
         </is>
       </c>
       <c r="CA51" s="9" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="CB51" s="4" t="inlineStr">
         <is>
@@ -16460,7 +16544,7 @@
         </is>
       </c>
       <c r="CF51" s="9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CG51" s="4" t="inlineStr">
         <is>
@@ -16476,7 +16560,7 @@
         </is>
       </c>
       <c r="CJ51" s="9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="CK51" s="10" t="inlineStr"/>
       <c r="CL51" s="10" t="inlineStr"/>
@@ -16494,7 +16578,7 @@
         </is>
       </c>
       <c r="CP51" s="9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="CQ51" s="8" t="inlineStr">
         <is>
@@ -16517,7 +16601,7 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
@@ -16541,7 +16625,7 @@
         </is>
       </c>
       <c r="I52" s="9" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -16563,7 +16647,7 @@
         </is>
       </c>
       <c r="S52" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T52" s="10" t="inlineStr"/>
       <c r="U52" s="10" t="inlineStr"/>
@@ -16593,7 +16677,7 @@
         </is>
       </c>
       <c r="AQ52" s="5" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AR52" s="4" t="inlineStr">
         <is>
@@ -16617,7 +16701,7 @@
         </is>
       </c>
       <c r="AW52" s="9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AX52" s="4" t="inlineStr">
         <is>
@@ -16731,7 +16815,7 @@
         </is>
       </c>
       <c r="CA52" s="9" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="CB52" s="4" t="inlineStr">
         <is>
@@ -16752,7 +16836,7 @@
         </is>
       </c>
       <c r="CF52" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CG52" s="4" t="inlineStr">
         <is>
@@ -16772,7 +16856,7 @@
         </is>
       </c>
       <c r="CN52" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CO52" s="8" t="inlineStr">
         <is>
@@ -16780,7 +16864,7 @@
         </is>
       </c>
       <c r="CP52" s="9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="CQ52" s="8" t="inlineStr">
         <is>
@@ -16803,15 +16887,15 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+        <v>1.43</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>0.049</v>
+        <v>0.06</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
@@ -16827,7 +16911,7 @@
         </is>
       </c>
       <c r="I53" s="9" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -16849,7 +16933,7 @@
         </is>
       </c>
       <c r="S53" s="5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="T53" s="10" t="inlineStr"/>
       <c r="U53" s="10" t="inlineStr"/>
@@ -16885,7 +16969,7 @@
         </is>
       </c>
       <c r="AW53" s="9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AX53" s="10" t="inlineStr"/>
       <c r="AY53" s="10" t="inlineStr"/>
@@ -16895,7 +16979,7 @@
         </is>
       </c>
       <c r="BA53" s="5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BB53" s="4" t="inlineStr">
         <is>
@@ -16969,7 +17053,7 @@
         </is>
       </c>
       <c r="BU53" s="5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BV53" s="4" t="inlineStr">
         <is>
@@ -16977,7 +17061,7 @@
         </is>
       </c>
       <c r="BW53" s="6" t="n">
-        <v>0.048</v>
+        <v>0.053</v>
       </c>
       <c r="BX53" s="4" t="inlineStr">
         <is>
@@ -16993,7 +17077,7 @@
         </is>
       </c>
       <c r="CA53" s="9" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="CB53" s="4" t="inlineStr">
         <is>
@@ -17014,7 +17098,7 @@
         </is>
       </c>
       <c r="CF53" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CG53" s="4" t="inlineStr">
         <is>
@@ -17028,21 +17112,21 @@
       <c r="CJ53" s="10" t="inlineStr"/>
       <c r="CK53" s="10" t="inlineStr"/>
       <c r="CL53" s="10" t="inlineStr"/>
-      <c r="CM53" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="CM53" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="CN53" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="CO53" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="CP53" s="9" t="n">
         <v>25</v>
-      </c>
-      <c r="CO53" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
-        </is>
-      </c>
-      <c r="CP53" s="9" t="n">
-        <v>26</v>
       </c>
       <c r="CQ53" s="8" t="inlineStr">
         <is>
@@ -17089,7 +17173,7 @@
         </is>
       </c>
       <c r="I54" s="9" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -17111,7 +17195,7 @@
         </is>
       </c>
       <c r="S54" s="5" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="T54" s="10" t="inlineStr"/>
       <c r="U54" s="10" t="inlineStr"/>
@@ -17165,7 +17249,7 @@
         </is>
       </c>
       <c r="BC54" s="6" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="BD54" s="4" t="inlineStr">
         <is>
@@ -17191,7 +17275,7 @@
         </is>
       </c>
       <c r="BK54" s="5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="BL54" s="4" t="inlineStr">
         <is>
@@ -17199,7 +17283,7 @@
         </is>
       </c>
       <c r="BM54" s="6" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="BN54" s="4" t="inlineStr">
         <is>
@@ -17215,7 +17299,7 @@
         </is>
       </c>
       <c r="BQ54" s="9" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BR54" s="4" t="inlineStr">
         <is>
@@ -17255,7 +17339,7 @@
         </is>
       </c>
       <c r="CA54" s="9" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="CB54" s="4" t="inlineStr">
         <is>
@@ -17276,7 +17360,7 @@
         </is>
       </c>
       <c r="CF54" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CG54" s="4" t="inlineStr">
         <is>
@@ -17290,13 +17374,13 @@
       <c r="CJ54" s="10" t="inlineStr"/>
       <c r="CK54" s="10" t="inlineStr"/>
       <c r="CL54" s="10" t="inlineStr"/>
-      <c r="CM54" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="CM54" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="CN54" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CO54" s="4" t="inlineStr">
         <is>
@@ -17312,7 +17396,7 @@
         </is>
       </c>
       <c r="CR54" s="9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CS54" s="10" t="inlineStr"/>
       <c r="CT54" s="10" t="inlineStr"/>
@@ -17351,7 +17435,7 @@
         </is>
       </c>
       <c r="I55" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -17403,7 +17487,7 @@
         </is>
       </c>
       <c r="AW55" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX55" s="10" t="inlineStr"/>
       <c r="AY55" s="10" t="inlineStr"/>
@@ -17465,7 +17549,7 @@
         </is>
       </c>
       <c r="BQ55" s="9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="BR55" s="4" t="inlineStr">
         <is>
@@ -17499,13 +17583,13 @@
       <c r="BY55" s="6" t="n">
         <v>0.053</v>
       </c>
-      <c r="BZ55" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="BZ55" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="CA55" s="9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="CB55" s="4" t="inlineStr">
         <is>
@@ -17526,7 +17610,7 @@
         </is>
       </c>
       <c r="CF55" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CG55" s="4" t="inlineStr">
         <is>
@@ -17595,7 +17679,7 @@
         </is>
       </c>
       <c r="I56" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -17647,7 +17731,7 @@
         </is>
       </c>
       <c r="AW56" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX56" s="10" t="inlineStr"/>
       <c r="AY56" s="10" t="inlineStr"/>
@@ -17709,7 +17793,7 @@
         </is>
       </c>
       <c r="BQ56" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="BR56" s="4" t="inlineStr">
         <is>
@@ -17749,7 +17833,7 @@
         </is>
       </c>
       <c r="CA56" s="9" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="CB56" s="4" t="inlineStr">
         <is>
@@ -17798,7 +17882,7 @@
         </is>
       </c>
       <c r="CP56" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CQ56" s="7" t="inlineStr">
         <is>
@@ -17821,7 +17905,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
@@ -17845,7 +17929,7 @@
         </is>
       </c>
       <c r="I57" s="9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -17853,7 +17937,7 @@
         </is>
       </c>
       <c r="K57" s="6" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="L57" s="10" t="inlineStr"/>
       <c r="M57" s="10" t="inlineStr"/>
@@ -17867,7 +17951,7 @@
         </is>
       </c>
       <c r="S57" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T57" s="10" t="inlineStr"/>
       <c r="U57" s="10" t="inlineStr"/>
@@ -17921,7 +18005,7 @@
         </is>
       </c>
       <c r="AW57" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AX57" s="10" t="inlineStr"/>
       <c r="AY57" s="10" t="inlineStr"/>
@@ -17989,7 +18073,7 @@
         </is>
       </c>
       <c r="BQ57" s="9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="BR57" s="4" t="inlineStr">
         <is>
@@ -18005,7 +18089,7 @@
         </is>
       </c>
       <c r="BU57" s="5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BV57" s="7" t="inlineStr">
         <is>
@@ -18029,7 +18113,7 @@
         </is>
       </c>
       <c r="CA57" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="CB57" s="4" t="inlineStr">
         <is>
@@ -18050,7 +18134,7 @@
         </is>
       </c>
       <c r="CF57" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CG57" s="4" t="inlineStr">
         <is>
@@ -18101,7 +18185,7 @@
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -18125,7 +18209,7 @@
         </is>
       </c>
       <c r="I58" s="9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -18147,7 +18231,7 @@
         </is>
       </c>
       <c r="S58" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T58" s="10" t="inlineStr"/>
       <c r="U58" s="10" t="inlineStr"/>
@@ -18157,7 +18241,7 @@
         </is>
       </c>
       <c r="W58" s="5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X58" s="4" t="inlineStr">
         <is>
@@ -18165,7 +18249,7 @@
         </is>
       </c>
       <c r="Y58" s="6" t="n">
-        <v>0.033</v>
+        <v>0.038</v>
       </c>
       <c r="Z58" s="7" t="inlineStr">
         <is>
@@ -18201,13 +18285,13 @@
       <c r="AS58" s="10" t="inlineStr"/>
       <c r="AT58" s="10" t="inlineStr"/>
       <c r="AU58" s="10" t="inlineStr"/>
-      <c r="AV58" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="AV58" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="AW58" s="9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AX58" s="10" t="inlineStr"/>
       <c r="AY58" s="10" t="inlineStr"/>
@@ -18241,7 +18325,7 @@
         </is>
       </c>
       <c r="BG58" s="9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BH58" s="10" t="inlineStr"/>
       <c r="BI58" s="10" t="inlineStr"/>
@@ -18275,7 +18359,7 @@
         </is>
       </c>
       <c r="BQ58" s="9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BR58" s="4" t="inlineStr">
         <is>
@@ -18291,7 +18375,7 @@
         </is>
       </c>
       <c r="BU58" s="5" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="BV58" s="7" t="inlineStr">
         <is>
@@ -18336,7 +18420,7 @@
         </is>
       </c>
       <c r="CF58" s="9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="CG58" s="4" t="inlineStr">
         <is>
@@ -18433,7 +18517,7 @@
         </is>
       </c>
       <c r="S59" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T59" s="10" t="inlineStr"/>
       <c r="U59" s="10" t="inlineStr"/>
@@ -18493,7 +18577,7 @@
         </is>
       </c>
       <c r="AW59" s="9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AX59" s="10" t="inlineStr"/>
       <c r="AY59" s="10" t="inlineStr"/>
@@ -18527,7 +18611,7 @@
         </is>
       </c>
       <c r="BG59" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BH59" s="10" t="inlineStr"/>
       <c r="BI59" s="10" t="inlineStr"/>
@@ -18585,7 +18669,7 @@
         </is>
       </c>
       <c r="BW59" s="6" t="n">
-        <v>0.037</v>
+        <v>0.047</v>
       </c>
       <c r="BX59" s="4" t="inlineStr">
         <is>
@@ -18601,7 +18685,7 @@
         </is>
       </c>
       <c r="CA59" s="9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="CB59" s="4" t="inlineStr">
         <is>
@@ -18622,7 +18706,7 @@
         </is>
       </c>
       <c r="CF59" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CG59" s="4" t="inlineStr">
         <is>
@@ -18644,13 +18728,13 @@
       <c r="CN59" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="CO59" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="CO59" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="CP59" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CQ59" s="7" t="inlineStr">
         <is>
@@ -18719,7 +18803,7 @@
         </is>
       </c>
       <c r="S60" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T60" s="10" t="inlineStr"/>
       <c r="U60" s="10" t="inlineStr"/>
@@ -18753,7 +18837,7 @@
         </is>
       </c>
       <c r="AC60" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AD60" s="4" t="inlineStr">
         <is>
@@ -18779,13 +18863,13 @@
       <c r="AS60" s="10" t="inlineStr"/>
       <c r="AT60" s="10" t="inlineStr"/>
       <c r="AU60" s="10" t="inlineStr"/>
-      <c r="AV60" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="AV60" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
         </is>
       </c>
       <c r="AW60" s="9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AX60" s="10" t="inlineStr"/>
       <c r="AY60" s="10" t="inlineStr"/>
@@ -18803,7 +18887,7 @@
         </is>
       </c>
       <c r="BC60" s="6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="BD60" s="4" t="inlineStr">
         <is>
@@ -18893,7 +18977,7 @@
         </is>
       </c>
       <c r="CA60" s="9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="CB60" s="4" t="inlineStr">
         <is>
@@ -18950,7 +19034,7 @@
         </is>
       </c>
       <c r="CR60" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CS60" s="10" t="inlineStr"/>
       <c r="CT60" s="10" t="inlineStr"/>
@@ -18965,7 +19049,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
@@ -18983,13 +19067,13 @@
       <c r="G61" s="6" t="n">
         <v>0.058</v>
       </c>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I61" s="9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -19077,7 +19161,7 @@
         </is>
       </c>
       <c r="AW61" s="9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AX61" s="10" t="inlineStr"/>
       <c r="AY61" s="10" t="inlineStr"/>
@@ -19121,7 +19205,7 @@
         </is>
       </c>
       <c r="BK61" s="5" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="BL61" s="4" t="inlineStr">
         <is>
@@ -19129,7 +19213,7 @@
         </is>
       </c>
       <c r="BM61" s="6" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="BN61" s="7" t="inlineStr">
         <is>
@@ -19145,7 +19229,7 @@
         </is>
       </c>
       <c r="BQ61" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BR61" s="4" t="inlineStr">
         <is>
@@ -19161,7 +19245,7 @@
         </is>
       </c>
       <c r="BU61" s="5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="BV61" s="4" t="inlineStr">
         <is>
@@ -19222,17 +19306,17 @@
         </is>
       </c>
       <c r="CJ61" s="9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CK61" s="10" t="inlineStr"/>
       <c r="CL61" s="10" t="inlineStr"/>
-      <c r="CM61" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="CM61" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="CN61" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CO61" s="10" t="inlineStr"/>
       <c r="CP61" s="10" t="inlineStr"/>
@@ -19281,7 +19365,7 @@
         </is>
       </c>
       <c r="I62" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -19303,7 +19387,7 @@
         </is>
       </c>
       <c r="S62" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T62" s="10" t="inlineStr"/>
       <c r="U62" s="10" t="inlineStr"/>
@@ -19337,7 +19421,7 @@
         </is>
       </c>
       <c r="AC62" s="9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AD62" s="4" t="inlineStr">
         <is>
@@ -19379,7 +19463,7 @@
         </is>
       </c>
       <c r="BA62" s="5" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BB62" s="4" t="inlineStr">
         <is>
@@ -19471,7 +19555,7 @@
         </is>
       </c>
       <c r="CA62" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="CB62" s="4" t="inlineStr">
         <is>
@@ -19492,7 +19576,7 @@
         </is>
       </c>
       <c r="CF62" s="9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CG62" s="4" t="inlineStr">
         <is>
@@ -19508,7 +19592,7 @@
         </is>
       </c>
       <c r="CJ62" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CK62" s="10" t="inlineStr"/>
       <c r="CL62" s="10" t="inlineStr"/>
@@ -19528,7 +19612,7 @@
         </is>
       </c>
       <c r="CR62" s="9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CS62" s="10" t="inlineStr"/>
       <c r="CT62" s="10" t="inlineStr"/>
@@ -19551,7 +19635,7 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
@@ -19567,7 +19651,7 @@
         </is>
       </c>
       <c r="I63" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -19589,7 +19673,7 @@
         </is>
       </c>
       <c r="S63" s="5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T63" s="10" t="inlineStr"/>
       <c r="U63" s="10" t="inlineStr"/>
@@ -19607,7 +19691,7 @@
         </is>
       </c>
       <c r="Y63" s="6" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="Z63" s="4" t="inlineStr">
         <is>
@@ -19623,7 +19707,7 @@
         </is>
       </c>
       <c r="AC63" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD63" s="4" t="inlineStr">
         <is>
@@ -19667,7 +19751,7 @@
         </is>
       </c>
       <c r="AW63" s="9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AX63" s="4" t="inlineStr">
         <is>
@@ -19711,13 +19795,13 @@
       <c r="BO63" s="6" t="n">
         <v>0.056</v>
       </c>
-      <c r="BP63" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="BP63" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="BQ63" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="BR63" s="4" t="inlineStr">
         <is>
@@ -19733,7 +19817,7 @@
         </is>
       </c>
       <c r="BU63" s="5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BV63" s="4" t="inlineStr">
         <is>
@@ -19757,7 +19841,7 @@
         </is>
       </c>
       <c r="CA63" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="CB63" s="4" t="inlineStr">
         <is>
@@ -19778,7 +19862,7 @@
         </is>
       </c>
       <c r="CF63" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CG63" s="4" t="inlineStr">
         <is>
@@ -19853,7 +19937,7 @@
         </is>
       </c>
       <c r="I64" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -19935,7 +20019,7 @@
         </is>
       </c>
       <c r="AQ64" s="5" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AR64" s="10" t="inlineStr"/>
       <c r="AS64" s="10" t="inlineStr"/>
@@ -20055,7 +20139,7 @@
         </is>
       </c>
       <c r="CA64" s="9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="CB64" s="4" t="inlineStr">
         <is>
@@ -20076,7 +20160,7 @@
         </is>
       </c>
       <c r="CF64" s="9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CG64" s="4" t="inlineStr">
         <is>
@@ -20092,7 +20176,7 @@
         </is>
       </c>
       <c r="CJ64" s="9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="CK64" s="10" t="inlineStr"/>
       <c r="CL64" s="10" t="inlineStr"/>
@@ -20207,7 +20291,7 @@
         </is>
       </c>
       <c r="AC65" s="9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD65" s="4" t="inlineStr">
         <is>
@@ -20273,7 +20357,7 @@
         </is>
       </c>
       <c r="BG65" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BH65" s="10" t="inlineStr"/>
       <c r="BI65" s="10" t="inlineStr"/>
@@ -20325,7 +20409,7 @@
         </is>
       </c>
       <c r="BW65" s="6" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="BX65" s="4" t="inlineStr">
         <is>
@@ -20341,7 +20425,7 @@
         </is>
       </c>
       <c r="CA65" s="9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="CB65" s="4" t="inlineStr">
         <is>
@@ -20390,13 +20474,13 @@
       <c r="CN65" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="CO65" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="CO65" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="CP65" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CQ65" s="10" t="inlineStr"/>
       <c r="CR65" s="10" t="inlineStr"/>
@@ -20437,7 +20521,7 @@
         </is>
       </c>
       <c r="I66" s="9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -20537,7 +20621,7 @@
         </is>
       </c>
       <c r="AW66" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AX66" s="4" t="inlineStr">
         <is>
@@ -20627,7 +20711,7 @@
         </is>
       </c>
       <c r="CA66" s="9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="CB66" s="4" t="inlineStr">
         <is>
@@ -20642,13 +20726,13 @@
           <t>Mala</t>
         </is>
       </c>
-      <c r="CE66" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="CE66" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="CF66" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CG66" s="4" t="inlineStr">
         <is>
@@ -20682,7 +20766,7 @@
         </is>
       </c>
       <c r="CP66" s="9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CQ66" s="10" t="inlineStr"/>
       <c r="CR66" s="10" t="inlineStr"/>
@@ -20699,7 +20783,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
@@ -20723,7 +20807,7 @@
         </is>
       </c>
       <c r="I67" s="9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -20823,7 +20907,7 @@
         </is>
       </c>
       <c r="AW67" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AX67" s="4" t="inlineStr">
         <is>
@@ -20845,7 +20929,7 @@
         </is>
       </c>
       <c r="BG67" s="9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="BH67" s="10" t="inlineStr"/>
       <c r="BI67" s="10" t="inlineStr"/>
@@ -20895,7 +20979,7 @@
         </is>
       </c>
       <c r="BU67" s="5" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BV67" s="4" t="inlineStr">
         <is>
@@ -20919,7 +21003,7 @@
         </is>
       </c>
       <c r="CA67" s="9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="CB67" s="4" t="inlineStr">
         <is>
@@ -20940,7 +21024,7 @@
         </is>
       </c>
       <c r="CF67" s="9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CG67" s="4" t="inlineStr">
         <is>
@@ -20966,7 +21050,7 @@
         </is>
       </c>
       <c r="CN67" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CO67" s="8" t="inlineStr">
         <is>
@@ -20974,7 +21058,7 @@
         </is>
       </c>
       <c r="CP67" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="CQ67" s="8" t="inlineStr">
         <is>
@@ -20997,7 +21081,7 @@
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
@@ -21021,7 +21105,7 @@
         </is>
       </c>
       <c r="I68" s="9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -21077,7 +21161,7 @@
         </is>
       </c>
       <c r="AC68" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AD68" s="4" t="inlineStr">
         <is>
@@ -21103,7 +21187,7 @@
         </is>
       </c>
       <c r="AQ68" s="5" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AR68" s="10" t="inlineStr"/>
       <c r="AS68" s="10" t="inlineStr"/>
@@ -21147,7 +21231,7 @@
         </is>
       </c>
       <c r="BK68" s="5" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="BL68" s="4" t="inlineStr">
         <is>
@@ -21155,7 +21239,7 @@
         </is>
       </c>
       <c r="BM68" s="6" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="BN68" s="7" t="inlineStr">
         <is>
@@ -21171,7 +21255,7 @@
         </is>
       </c>
       <c r="BQ68" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BR68" s="4" t="inlineStr">
         <is>
@@ -21187,7 +21271,7 @@
         </is>
       </c>
       <c r="BU68" s="5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BV68" s="4" t="inlineStr">
         <is>
@@ -21195,7 +21279,7 @@
         </is>
       </c>
       <c r="BW68" s="6" t="n">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
       <c r="BX68" s="4" t="inlineStr">
         <is>
@@ -21211,7 +21295,7 @@
         </is>
       </c>
       <c r="CA68" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="CB68" s="4" t="inlineStr">
         <is>
@@ -21232,7 +21316,7 @@
         </is>
       </c>
       <c r="CF68" s="9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CG68" s="4" t="inlineStr">
         <is>
@@ -21643,7 +21727,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
@@ -21667,7 +21751,7 @@
         </is>
       </c>
       <c r="I3" s="9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -21693,7 +21777,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -21701,7 +21785,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.039</v>
+        <v>0.048</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -21717,7 +21801,7 @@
         </is>
       </c>
       <c r="I4" s="9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -21751,7 +21835,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -21843,7 +21927,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -21867,7 +21951,7 @@
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -21917,7 +22001,7 @@
         </is>
       </c>
       <c r="I8" s="9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -21943,7 +22027,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -21967,7 +22051,7 @@
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -21993,7 +22077,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -22017,7 +22101,7 @@
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -22043,7 +22127,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -22067,7 +22151,7 @@
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -22075,7 +22159,7 @@
         </is>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -22117,7 +22201,7 @@
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -22151,7 +22235,7 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -22177,9 +22261,9 @@
       <c r="K13" s="6" t="n">
         <v>0.002</v>
       </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
         </is>
       </c>
     </row>
@@ -22217,7 +22301,7 @@
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -22227,9 +22311,9 @@
       <c r="K14" s="6" t="n">
         <v>0.003</v>
       </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
         </is>
       </c>
     </row>
@@ -22293,7 +22377,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -22327,9 +22411,9 @@
       <c r="K16" s="6" t="n">
         <v>0.001</v>
       </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22367,7 +22451,7 @@
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -22411,13 +22495,13 @@
       <c r="G18" s="6" t="n">
         <v>0.061</v>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -22443,7 +22527,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
@@ -22451,7 +22535,7 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -22467,7 +22551,7 @@
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -22475,7 +22559,7 @@
         </is>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -22517,7 +22601,7 @@
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -22567,7 +22651,7 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -22693,7 +22777,7 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
@@ -22701,7 +22785,7 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.031</v>
+        <v>0.034</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -22717,7 +22801,7 @@
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -22967,7 +23051,7 @@
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -23017,7 +23101,7 @@
         </is>
       </c>
       <c r="I30" s="9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -23043,7 +23127,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
@@ -23051,7 +23135,7 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.047</v>
+        <v>0.052</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
@@ -23067,7 +23151,7 @@
         </is>
       </c>
       <c r="I31" s="9" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -23093,7 +23177,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
@@ -23167,7 +23251,7 @@
         </is>
       </c>
       <c r="I33" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -23267,7 +23351,7 @@
         </is>
       </c>
       <c r="I35" s="9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -23317,7 +23401,7 @@
         </is>
       </c>
       <c r="I36" s="9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -23467,7 +23551,7 @@
         </is>
       </c>
       <c r="I39" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -23493,7 +23577,7 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
@@ -23501,7 +23585,7 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
@@ -23517,7 +23601,7 @@
         </is>
       </c>
       <c r="I40" s="9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -23617,7 +23701,7 @@
         </is>
       </c>
       <c r="I42" s="9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -23643,7 +23727,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -23651,7 +23735,7 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.041</v>
+        <v>0.05</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
@@ -23667,7 +23751,7 @@
         </is>
       </c>
       <c r="I43" s="9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -23817,7 +23901,7 @@
         </is>
       </c>
       <c r="I46" s="9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -23843,7 +23927,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
@@ -23851,7 +23935,7 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>0.056</v>
+        <v>0.06</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -23867,7 +23951,7 @@
         </is>
       </c>
       <c r="I47" s="9" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -23917,7 +24001,7 @@
         </is>
       </c>
       <c r="I48" s="9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -23967,7 +24051,7 @@
         </is>
       </c>
       <c r="I49" s="9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -24043,7 +24127,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
@@ -24061,8 +24145,14 @@
       <c r="G51" s="6" t="n">
         <v>0.068</v>
       </c>
-      <c r="H51" s="10" t="inlineStr"/>
-      <c r="I51" s="10" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="n">
+        <v>91</v>
+      </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>Buena</t>
@@ -24087,7 +24177,7 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
@@ -24111,7 +24201,7 @@
         </is>
       </c>
       <c r="I52" s="9" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -24137,15 +24227,15 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+        <v>1.43</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>0.049</v>
+        <v>0.06</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
@@ -24161,7 +24251,7 @@
         </is>
       </c>
       <c r="I53" s="9" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -24211,7 +24301,7 @@
         </is>
       </c>
       <c r="I54" s="9" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -24261,7 +24351,7 @@
         </is>
       </c>
       <c r="I55" s="9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -24311,7 +24401,7 @@
         </is>
       </c>
       <c r="I56" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -24337,7 +24427,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
@@ -24361,7 +24451,7 @@
         </is>
       </c>
       <c r="I57" s="9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -24369,7 +24459,7 @@
         </is>
       </c>
       <c r="K57" s="6" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -24387,7 +24477,7 @@
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -24411,7 +24501,7 @@
         </is>
       </c>
       <c r="I58" s="9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -24537,7 +24627,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
@@ -24555,13 +24645,13 @@
       <c r="G61" s="6" t="n">
         <v>0.058</v>
       </c>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I61" s="9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -24571,9 +24661,9 @@
       <c r="K61" s="6" t="n">
         <v>0.003</v>
       </c>
-      <c r="L61" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -24611,7 +24701,7 @@
         </is>
       </c>
       <c r="I62" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -24645,7 +24735,7 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
@@ -24661,7 +24751,7 @@
         </is>
       </c>
       <c r="I63" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -24711,7 +24801,7 @@
         </is>
       </c>
       <c r="I64" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -24811,7 +24901,7 @@
         </is>
       </c>
       <c r="I66" s="9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -24821,9 +24911,9 @@
       <c r="K66" s="6" t="n">
         <v>0.004</v>
       </c>
-      <c r="L66" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -24837,7 +24927,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
@@ -24861,7 +24951,7 @@
         </is>
       </c>
       <c r="I67" s="9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -24887,7 +24977,7 @@
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
@@ -24911,7 +25001,7 @@
         </is>
       </c>
       <c r="I68" s="9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -25095,7 +25185,7 @@
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" s="10" t="inlineStr"/>
       <c r="K3" s="10" t="inlineStr"/>
@@ -25117,7 +25207,7 @@
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J4" s="10" t="inlineStr"/>
       <c r="K4" s="10" t="inlineStr"/>
@@ -25139,7 +25229,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J5" s="10" t="inlineStr"/>
       <c r="K5" s="10" t="inlineStr"/>
@@ -25155,13 +25245,13 @@
       <c r="E6" s="10" t="inlineStr"/>
       <c r="F6" s="10" t="inlineStr"/>
       <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J6" s="10" t="inlineStr"/>
       <c r="K6" s="10" t="inlineStr"/>
@@ -25177,13 +25267,13 @@
       <c r="E7" s="10" t="inlineStr"/>
       <c r="F7" s="10" t="inlineStr"/>
       <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J7" s="10" t="inlineStr"/>
       <c r="K7" s="10" t="inlineStr"/>
@@ -25227,7 +25317,7 @@
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J9" s="10" t="inlineStr"/>
       <c r="K9" s="10" t="inlineStr"/>
@@ -25249,7 +25339,7 @@
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J10" s="10" t="inlineStr"/>
       <c r="K10" s="10" t="inlineStr"/>
@@ -25271,7 +25361,7 @@
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J11" s="10" t="inlineStr"/>
       <c r="K11" s="10" t="inlineStr"/>
@@ -25325,7 +25415,7 @@
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J14" s="10" t="inlineStr"/>
       <c r="K14" s="10" t="inlineStr"/>
@@ -25385,13 +25475,13 @@
       <c r="E17" s="10" t="inlineStr"/>
       <c r="F17" s="10" t="inlineStr"/>
       <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J17" s="10" t="inlineStr"/>
       <c r="K17" s="10" t="inlineStr"/>
@@ -25413,7 +25503,7 @@
         </is>
       </c>
       <c r="I18" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J18" s="10" t="inlineStr"/>
       <c r="K18" s="10" t="inlineStr"/>
@@ -25435,7 +25525,7 @@
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J19" s="10" t="inlineStr"/>
       <c r="K19" s="10" t="inlineStr"/>
@@ -25451,8 +25541,14 @@
       <c r="E20" s="10" t="inlineStr"/>
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="10" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>39</v>
+      </c>
       <c r="J20" s="10" t="inlineStr"/>
       <c r="K20" s="10" t="inlineStr"/>
       <c r="L20" s="10" t="inlineStr"/>
@@ -25533,7 +25629,7 @@
         </is>
       </c>
       <c r="I24" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J24" s="10" t="inlineStr"/>
       <c r="K24" s="10" t="inlineStr"/>
@@ -25577,7 +25673,7 @@
         </is>
       </c>
       <c r="I26" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J26" s="10" t="inlineStr"/>
       <c r="K26" s="10" t="inlineStr"/>
@@ -25599,7 +25695,7 @@
         </is>
       </c>
       <c r="I27" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J27" s="10" t="inlineStr"/>
       <c r="K27" s="10" t="inlineStr"/>
@@ -25637,7 +25733,7 @@
         </is>
       </c>
       <c r="I29" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J29" s="10" t="inlineStr"/>
       <c r="K29" s="10" t="inlineStr"/>
@@ -25703,7 +25799,7 @@
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J32" s="10" t="inlineStr"/>
       <c r="K32" s="10" t="inlineStr"/>
@@ -25725,7 +25821,7 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J33" s="10" t="inlineStr"/>
       <c r="K33" s="10" t="inlineStr"/>
@@ -25741,8 +25837,14 @@
       <c r="E34" s="10" t="inlineStr"/>
       <c r="F34" s="10" t="inlineStr"/>
       <c r="G34" s="10" t="inlineStr"/>
-      <c r="H34" s="10" t="inlineStr"/>
-      <c r="I34" s="10" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>44</v>
+      </c>
       <c r="J34" s="10" t="inlineStr"/>
       <c r="K34" s="10" t="inlineStr"/>
       <c r="L34" s="10" t="inlineStr"/>
@@ -25785,7 +25887,7 @@
         </is>
       </c>
       <c r="I36" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J36" s="10" t="inlineStr"/>
       <c r="K36" s="10" t="inlineStr"/>
@@ -25801,8 +25903,14 @@
       <c r="E37" s="10" t="inlineStr"/>
       <c r="F37" s="10" t="inlineStr"/>
       <c r="G37" s="10" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr"/>
-      <c r="I37" s="10" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>46</v>
+      </c>
       <c r="J37" s="10" t="inlineStr"/>
       <c r="K37" s="10" t="inlineStr"/>
       <c r="L37" s="10" t="inlineStr"/>
@@ -25823,7 +25931,7 @@
         </is>
       </c>
       <c r="I38" s="5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J38" s="10" t="inlineStr"/>
       <c r="K38" s="10" t="inlineStr"/>
@@ -25839,13 +25947,13 @@
       <c r="E39" s="10" t="inlineStr"/>
       <c r="F39" s="10" t="inlineStr"/>
       <c r="G39" s="10" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J39" s="10" t="inlineStr"/>
       <c r="K39" s="10" t="inlineStr"/>
@@ -25867,7 +25975,7 @@
         </is>
       </c>
       <c r="I40" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J40" s="10" t="inlineStr"/>
       <c r="K40" s="10" t="inlineStr"/>
@@ -25883,13 +25991,13 @@
       <c r="E41" s="10" t="inlineStr"/>
       <c r="F41" s="10" t="inlineStr"/>
       <c r="G41" s="10" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I41" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J41" s="10" t="inlineStr"/>
       <c r="K41" s="10" t="inlineStr"/>
@@ -25911,7 +26019,7 @@
         </is>
       </c>
       <c r="I42" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J42" s="10" t="inlineStr"/>
       <c r="K42" s="10" t="inlineStr"/>
@@ -25933,7 +26041,7 @@
         </is>
       </c>
       <c r="I43" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J43" s="10" t="inlineStr"/>
       <c r="K43" s="10" t="inlineStr"/>
@@ -25955,7 +26063,7 @@
         </is>
       </c>
       <c r="I44" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J44" s="10" t="inlineStr"/>
       <c r="K44" s="10" t="inlineStr"/>
@@ -25977,7 +26085,7 @@
         </is>
       </c>
       <c r="I45" s="5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J45" s="10" t="inlineStr"/>
       <c r="K45" s="10" t="inlineStr"/>
@@ -26021,7 +26129,7 @@
         </is>
       </c>
       <c r="I47" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J47" s="10" t="inlineStr"/>
       <c r="K47" s="10" t="inlineStr"/>
@@ -26043,7 +26151,7 @@
         </is>
       </c>
       <c r="I48" s="5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J48" s="10" t="inlineStr"/>
       <c r="K48" s="10" t="inlineStr"/>
@@ -26065,7 +26173,7 @@
         </is>
       </c>
       <c r="I49" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J49" s="10" t="inlineStr"/>
       <c r="K49" s="10" t="inlineStr"/>
@@ -26087,7 +26195,7 @@
         </is>
       </c>
       <c r="I50" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J50" s="10" t="inlineStr"/>
       <c r="K50" s="10" t="inlineStr"/>
@@ -26109,7 +26217,7 @@
         </is>
       </c>
       <c r="I51" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J51" s="10" t="inlineStr"/>
       <c r="K51" s="10" t="inlineStr"/>
@@ -26131,7 +26239,7 @@
         </is>
       </c>
       <c r="I52" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J52" s="10" t="inlineStr"/>
       <c r="K52" s="10" t="inlineStr"/>
@@ -26153,7 +26261,7 @@
         </is>
       </c>
       <c r="I53" s="5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J53" s="10" t="inlineStr"/>
       <c r="K53" s="10" t="inlineStr"/>
@@ -26175,7 +26283,7 @@
         </is>
       </c>
       <c r="I54" s="5" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J54" s="10" t="inlineStr"/>
       <c r="K54" s="10" t="inlineStr"/>
@@ -26229,7 +26337,7 @@
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J57" s="10" t="inlineStr"/>
       <c r="K57" s="10" t="inlineStr"/>
@@ -26251,7 +26359,7 @@
         </is>
       </c>
       <c r="I58" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J58" s="10" t="inlineStr"/>
       <c r="K58" s="10" t="inlineStr"/>
@@ -26273,7 +26381,7 @@
         </is>
       </c>
       <c r="I59" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J59" s="10" t="inlineStr"/>
       <c r="K59" s="10" t="inlineStr"/>
@@ -26295,7 +26403,7 @@
         </is>
       </c>
       <c r="I60" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J60" s="10" t="inlineStr"/>
       <c r="K60" s="10" t="inlineStr"/>
@@ -26339,7 +26447,7 @@
         </is>
       </c>
       <c r="I62" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J62" s="10" t="inlineStr"/>
       <c r="K62" s="10" t="inlineStr"/>
@@ -26361,7 +26469,7 @@
         </is>
       </c>
       <c r="I63" s="5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J63" s="10" t="inlineStr"/>
       <c r="K63" s="10" t="inlineStr"/>
@@ -26667,7 +26775,7 @@
         </is>
       </c>
       <c r="I3" s="9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -26677,9 +26785,9 @@
       <c r="K3" s="6" t="n">
         <v>0.005</v>
       </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
     </row>
@@ -26693,7 +26801,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -26701,7 +26809,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.026</v>
+        <v>0.045</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -26717,7 +26825,7 @@
         </is>
       </c>
       <c r="I4" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -26843,7 +26951,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -26851,7 +26959,7 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
@@ -26861,13 +26969,13 @@
       <c r="G7" s="6" t="n">
         <v>0.101</v>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -26943,7 +27051,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -26967,7 +27075,7 @@
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -27033,7 +27141,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -27041,7 +27149,7 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -27057,7 +27165,7 @@
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -27065,7 +27173,7 @@
         </is>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -27157,7 +27265,7 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -27257,7 +27365,7 @@
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -27283,7 +27391,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -27307,7 +27415,7 @@
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -27357,7 +27465,7 @@
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -27383,7 +27491,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
@@ -27407,7 +27515,7 @@
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -27441,7 +27549,7 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -27457,7 +27565,7 @@
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -27507,7 +27615,7 @@
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -27517,9 +27625,9 @@
       <c r="K20" s="6" t="n">
         <v>0.003</v>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -27551,13 +27659,13 @@
       <c r="G21" s="6" t="n">
         <v>0.056</v>
       </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -27567,9 +27675,9 @@
       <c r="K21" s="6" t="n">
         <v>0.004</v>
       </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -27607,7 +27715,7 @@
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -27691,7 +27799,7 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
@@ -27869,7 +27977,7 @@
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -27919,7 +28027,7 @@
         </is>
       </c>
       <c r="I30" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -27945,7 +28053,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
@@ -27969,7 +28077,7 @@
         </is>
       </c>
       <c r="I31" s="9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -28119,7 +28227,7 @@
         </is>
       </c>
       <c r="I34" s="9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -28379,7 +28487,7 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
@@ -28463,9 +28571,9 @@
       <c r="K41" s="6" t="n">
         <v>0.005</v>
       </c>
-      <c r="L41" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28605,7 @@
         </is>
       </c>
       <c r="I42" s="9" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
@@ -28519,7 +28627,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -28543,7 +28651,7 @@
         </is>
       </c>
       <c r="I43" s="9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -28643,7 +28751,7 @@
         </is>
       </c>
       <c r="I45" s="9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -28777,7 +28885,7 @@
         </is>
       </c>
       <c r="I48" s="9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -28895,7 +29003,7 @@
         </is>
       </c>
       <c r="I51" s="9" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J51" s="10" t="inlineStr"/>
       <c r="K51" s="10" t="inlineStr"/>
@@ -29025,7 +29133,7 @@
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
@@ -29033,7 +29141,7 @@
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>0.033</v>
+        <v>0.038</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
@@ -29129,7 +29237,7 @@
         </is>
       </c>
       <c r="I60" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -29229,7 +29337,7 @@
         </is>
       </c>
       <c r="I62" s="9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -29263,7 +29371,7 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
@@ -29279,7 +29387,7 @@
         </is>
       </c>
       <c r="I63" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -29379,7 +29487,7 @@
         </is>
       </c>
       <c r="I65" s="9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
@@ -29529,7 +29637,7 @@
         </is>
       </c>
       <c r="I68" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -30963,7 +31071,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -30987,7 +31095,7 @@
         </is>
       </c>
       <c r="I4" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -31021,7 +31129,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -31037,7 +31145,7 @@
         </is>
       </c>
       <c r="I5" s="9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -31087,7 +31195,7 @@
         </is>
       </c>
       <c r="I6" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -31113,7 +31221,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -31137,7 +31245,7 @@
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -31187,7 +31295,7 @@
         </is>
       </c>
       <c r="I8" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -31263,7 +31371,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -31287,7 +31395,7 @@
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -31313,7 +31421,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -31363,7 +31471,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -31379,7 +31487,7 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -31387,7 +31495,7 @@
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -31437,7 +31545,7 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -31487,7 +31595,7 @@
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -31513,7 +31621,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
@@ -31521,7 +31629,7 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -31537,7 +31645,7 @@
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -31587,7 +31695,7 @@
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -31629,7 +31737,7 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
@@ -31637,7 +31745,7 @@
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -31663,15 +31771,15 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+        <v>2.17</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.041</v>
+        <v>0.057</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -31687,7 +31795,7 @@
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -31713,7 +31821,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
@@ -31813,7 +31921,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -31887,7 +31995,7 @@
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -31913,7 +32021,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -32021,7 +32129,7 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.043</v>
+        <v>0.048</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
@@ -32037,7 +32145,7 @@
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -32087,7 +32195,7 @@
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -32113,7 +32221,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
@@ -32121,7 +32229,7 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
@@ -32237,7 +32345,7 @@
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -32287,7 +32395,7 @@
         </is>
       </c>
       <c r="I30" s="9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -32313,7 +32421,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
@@ -32321,7 +32429,7 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.037</v>
+        <v>0.049</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
@@ -32337,7 +32445,7 @@
         </is>
       </c>
       <c r="I31" s="9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -32363,7 +32471,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
@@ -32387,7 +32495,7 @@
         </is>
       </c>
       <c r="I32" s="9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -32413,7 +32521,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
@@ -32513,7 +32621,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -32563,15 +32671,15 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+        <v>2.7</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.047</v>
+        <v>0.059</v>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
@@ -32587,7 +32695,7 @@
         </is>
       </c>
       <c r="I36" s="9" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -32687,7 +32795,7 @@
         </is>
       </c>
       <c r="I38" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -32737,7 +32845,7 @@
         </is>
       </c>
       <c r="I39" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -32781,13 +32889,13 @@
       <c r="G40" s="6" t="n">
         <v>0.031</v>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I40" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -32831,13 +32939,13 @@
       <c r="G41" s="6" t="n">
         <v>0.028</v>
       </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="I41" s="9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -32847,9 +32955,9 @@
       <c r="K41" s="6" t="n">
         <v>0.003</v>
       </c>
-      <c r="L41" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
     </row>
@@ -32913,7 +33021,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
@@ -32921,7 +33029,7 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.058</v>
+        <v>0.066</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
@@ -32937,7 +33045,7 @@
         </is>
       </c>
       <c r="I43" s="9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -33037,7 +33145,7 @@
         </is>
       </c>
       <c r="I45" s="9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -33063,7 +33171,7 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
@@ -33087,7 +33195,7 @@
         </is>
       </c>
       <c r="I46" s="9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -33113,7 +33221,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
@@ -33121,7 +33229,7 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>0.055</v>
+        <v>0.078</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
@@ -33137,7 +33245,7 @@
         </is>
       </c>
       <c r="I47" s="9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -33187,7 +33295,7 @@
         </is>
       </c>
       <c r="I48" s="9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -33237,7 +33345,7 @@
         </is>
       </c>
       <c r="I49" s="9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -33287,7 +33395,7 @@
         </is>
       </c>
       <c r="I50" s="9" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -33313,7 +33421,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
@@ -33321,7 +33429,7 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0.042</v>
+        <v>0.046</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
@@ -33337,7 +33445,7 @@
         </is>
       </c>
       <c r="I51" s="9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -33363,7 +33471,7 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
@@ -33387,7 +33495,7 @@
         </is>
       </c>
       <c r="I52" s="9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -33419,7 +33527,7 @@
         </is>
       </c>
       <c r="I53" s="9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J53" s="10" t="inlineStr"/>
       <c r="K53" s="10" t="inlineStr"/>
@@ -33463,7 +33571,7 @@
         </is>
       </c>
       <c r="I55" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J55" s="10" t="inlineStr"/>
       <c r="K55" s="10" t="inlineStr"/>
@@ -33485,7 +33593,7 @@
         </is>
       </c>
       <c r="I56" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J56" s="10" t="inlineStr"/>
       <c r="K56" s="10" t="inlineStr"/>
@@ -33507,7 +33615,7 @@
         </is>
       </c>
       <c r="I57" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J57" s="10" t="inlineStr"/>
       <c r="K57" s="10" t="inlineStr"/>
@@ -33523,13 +33631,13 @@
       <c r="E58" s="10" t="inlineStr"/>
       <c r="F58" s="10" t="inlineStr"/>
       <c r="G58" s="10" t="inlineStr"/>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Mala</t>
         </is>
       </c>
       <c r="I58" s="9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J58" s="10" t="inlineStr"/>
       <c r="K58" s="10" t="inlineStr"/>
@@ -33551,7 +33659,7 @@
         </is>
       </c>
       <c r="I59" s="9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J59" s="10" t="inlineStr"/>
       <c r="K59" s="10" t="inlineStr"/>
@@ -33567,13 +33675,13 @@
       <c r="E60" s="10" t="inlineStr"/>
       <c r="F60" s="10" t="inlineStr"/>
       <c r="G60" s="10" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
         </is>
       </c>
       <c r="I60" s="9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J60" s="10" t="inlineStr"/>
       <c r="K60" s="10" t="inlineStr"/>
@@ -33595,7 +33703,7 @@
         </is>
       </c>
       <c r="I61" s="9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J61" s="10" t="inlineStr"/>
       <c r="K61" s="10" t="inlineStr"/>
@@ -33651,7 +33759,7 @@
         </is>
       </c>
       <c r="I63" s="9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -33677,7 +33785,7 @@
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="D64" s="10" t="inlineStr"/>
       <c r="E64" s="10" t="inlineStr"/>
@@ -33783,7 +33891,7 @@
         </is>
       </c>
       <c r="I66" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -33827,7 +33935,7 @@
         </is>
       </c>
       <c r="I67" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -33853,7 +33961,7 @@
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="D68" s="10" t="inlineStr"/>
       <c r="E68" s="10" t="inlineStr"/>
@@ -34115,7 +34223,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -34203,7 +34311,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -34227,7 +34335,7 @@
         </is>
       </c>
       <c r="I6" s="9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J6" s="10" t="inlineStr"/>
       <c r="K6" s="10" t="inlineStr"/>
@@ -34247,7 +34355,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -34271,7 +34379,7 @@
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7" s="10" t="inlineStr"/>
       <c r="K7" s="10" t="inlineStr"/>
@@ -34387,7 +34495,7 @@
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -34421,7 +34529,7 @@
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -34495,7 +34603,7 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -34521,7 +34629,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
@@ -34541,8 +34649,14 @@
       </c>
       <c r="H14" s="10" t="inlineStr"/>
       <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>0.001</v>
+      </c>
       <c r="L14" s="10" t="inlineStr"/>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -34613,8 +34727,14 @@
       <c r="G16" s="6" t="n">
         <v>0.051</v>
       </c>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Buena</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>29</v>
+      </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Buena</t>
@@ -34807,7 +34927,7 @@
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -34833,7 +34953,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -34857,7 +34977,7 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -34891,7 +35011,7 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
@@ -35183,7 +35303,7 @@
         </is>
       </c>
       <c r="I28" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -35209,7 +35329,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
@@ -35277,7 +35397,7 @@
         </is>
       </c>
       <c r="I30" s="9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J30" s="10" t="inlineStr"/>
       <c r="K30" s="10" t="inlineStr"/>
@@ -35365,7 +35485,7 @@
         </is>
       </c>
       <c r="I32" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J32" s="10" t="inlineStr"/>
       <c r="K32" s="10" t="inlineStr"/>
@@ -35409,7 +35529,7 @@
         </is>
       </c>
       <c r="I33" s="9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J33" s="10" t="inlineStr"/>
       <c r="K33" s="10" t="inlineStr"/>
@@ -35473,7 +35593,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
@@ -35497,7 +35617,7 @@
         </is>
       </c>
       <c r="I35" s="9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J35" s="10" t="inlineStr"/>
       <c r="K35" s="10" t="inlineStr"/>
@@ -35541,7 +35661,7 @@
         </is>
       </c>
       <c r="I36" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J36" s="10" t="inlineStr"/>
       <c r="K36" s="10" t="inlineStr"/>
@@ -35585,7 +35705,7 @@
         </is>
       </c>
       <c r="I37" s="9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J37" s="10" t="inlineStr"/>
       <c r="K37" s="10" t="inlineStr"/>
@@ -35679,7 +35799,7 @@
         </is>
       </c>
       <c r="I39" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J39" s="10" t="inlineStr"/>
       <c r="K39" s="10" t="inlineStr"/>
@@ -35767,7 +35887,7 @@
         </is>
       </c>
       <c r="I41" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J41" s="10" t="inlineStr"/>
       <c r="K41" s="10" t="inlineStr"/>
@@ -35787,7 +35907,7 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
@@ -35831,7 +35951,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -35987,7 +36107,7 @@
         </is>
       </c>
       <c r="I46" s="9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J46" s="10" t="inlineStr"/>
       <c r="K46" s="10" t="inlineStr"/>
@@ -36031,7 +36151,7 @@
         </is>
       </c>
       <c r="I47" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J47" s="10" t="inlineStr"/>
       <c r="K47" s="10" t="inlineStr"/>
@@ -36197,7 +36317,7 @@
         </is>
       </c>
       <c r="I51" s="9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J51" s="10" t="inlineStr"/>
       <c r="K51" s="10" t="inlineStr"/>
@@ -36261,7 +36381,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
@@ -36289,9 +36409,9 @@
       </c>
       <c r="J53" s="10" t="inlineStr"/>
       <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -36313,7 +36433,7 @@
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
@@ -36485,7 +36605,7 @@
         </is>
       </c>
       <c r="I58" s="9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J58" s="10" t="inlineStr"/>
       <c r="K58" s="10" t="inlineStr"/>
@@ -36529,13 +36649,13 @@
         </is>
       </c>
       <c r="I59" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J59" s="10" t="inlineStr"/>
       <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -36557,7 +36677,7 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
@@ -36629,7 +36749,7 @@
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
@@ -36713,7 +36833,7 @@
         </is>
       </c>
       <c r="I65" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J65" s="10" t="inlineStr"/>
       <c r="K65" s="10" t="inlineStr"/>
@@ -36757,7 +36877,7 @@
         </is>
       </c>
       <c r="I67" s="9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J67" s="10" t="inlineStr"/>
       <c r="K67" s="10" t="inlineStr"/>
@@ -36969,7 +37089,7 @@
         </is>
       </c>
       <c r="I3" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -37269,7 +37389,7 @@
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -37295,7 +37415,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -37319,7 +37439,7 @@
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -37345,7 +37465,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -37369,7 +37489,7 @@
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -37419,7 +37539,7 @@
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -37469,7 +37589,7 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -37519,7 +37639,7 @@
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -37595,7 +37715,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -37603,7 +37723,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -37619,7 +37739,7 @@
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -37669,7 +37789,7 @@
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -37695,7 +37815,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
@@ -37719,7 +37839,7 @@
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -37745,7 +37865,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
@@ -37753,7 +37873,7 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -37769,7 +37889,7 @@
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -37869,7 +37989,7 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -37919,7 +38039,7 @@
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -38059,7 +38179,7 @@
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -38085,7 +38205,7 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
@@ -38109,7 +38229,7 @@
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -38135,7 +38255,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
@@ -38259,7 +38379,7 @@
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -38309,7 +38429,7 @@
         </is>
       </c>
       <c r="I30" s="9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -38385,7 +38505,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
@@ -38509,7 +38629,7 @@
         </is>
       </c>
       <c r="I34" s="9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -38559,7 +38679,7 @@
         </is>
       </c>
       <c r="I35" s="9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -38609,7 +38729,7 @@
         </is>
       </c>
       <c r="I36" s="9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -38635,7 +38755,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
@@ -38783,7 +38903,7 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
@@ -38793,13 +38913,13 @@
       <c r="G40" s="6" t="n">
         <v>0.074</v>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I40" s="9" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -38849,7 +38969,7 @@
         </is>
       </c>
       <c r="I41" s="9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -38899,7 +39019,7 @@
         </is>
       </c>
       <c r="I42" s="9" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J42" s="10" t="inlineStr"/>
       <c r="K42" s="10" t="inlineStr"/>
@@ -38943,7 +39063,7 @@
         </is>
       </c>
       <c r="I43" s="9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -39037,7 +39157,7 @@
         </is>
       </c>
       <c r="I45" s="9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J45" s="10" t="inlineStr"/>
       <c r="K45" s="10" t="inlineStr"/>
@@ -39101,7 +39221,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
@@ -39125,7 +39245,7 @@
         </is>
       </c>
       <c r="I47" s="9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J47" s="10" t="inlineStr"/>
       <c r="K47" s="10" t="inlineStr"/>
@@ -39213,7 +39333,7 @@
         </is>
       </c>
       <c r="I49" s="9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -39263,7 +39383,7 @@
         </is>
       </c>
       <c r="I50" s="9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -39313,7 +39433,7 @@
         </is>
       </c>
       <c r="I51" s="9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -39439,7 +39559,7 @@
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
@@ -39447,7 +39567,7 @@
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
@@ -39463,7 +39583,7 @@
         </is>
       </c>
       <c r="I54" s="9" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -39513,7 +39633,7 @@
         </is>
       </c>
       <c r="I55" s="9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -39563,7 +39683,7 @@
         </is>
       </c>
       <c r="I56" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -39613,7 +39733,7 @@
         </is>
       </c>
       <c r="I57" s="9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -39663,7 +39783,7 @@
         </is>
       </c>
       <c r="I58" s="9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -39789,7 +39909,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
@@ -39797,7 +39917,7 @@
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
@@ -39813,7 +39933,7 @@
         </is>
       </c>
       <c r="I61" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -39907,13 +40027,13 @@
       <c r="G63" s="6" t="n">
         <v>0.056</v>
       </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>Buena</t>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I63" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -40119,7 +40239,7 @@
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
@@ -40127,7 +40247,7 @@
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
@@ -40143,7 +40263,7 @@
         </is>
       </c>
       <c r="I68" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -40339,7 +40459,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="D3" s="10" t="inlineStr"/>
       <c r="E3" s="10" t="inlineStr"/>
@@ -40379,7 +40499,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="D4" s="10" t="inlineStr"/>
       <c r="E4" s="10" t="inlineStr"/>
@@ -40397,7 +40517,7 @@
         </is>
       </c>
       <c r="I4" s="9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -40477,7 +40597,7 @@
         </is>
       </c>
       <c r="I6" s="9" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -40499,7 +40619,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
       <c r="E7" s="10" t="inlineStr"/>
@@ -40517,7 +40637,7 @@
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -40557,7 +40677,7 @@
         </is>
       </c>
       <c r="I8" s="9" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -40579,7 +40699,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="10" t="inlineStr"/>
@@ -40597,7 +40717,7 @@
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -40637,7 +40757,7 @@
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -40677,7 +40797,7 @@
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -40757,7 +40877,7 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -40837,7 +40957,7 @@
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -40877,7 +40997,7 @@
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -40899,7 +41019,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
       <c r="E17" s="10" t="inlineStr"/>
@@ -40917,7 +41037,7 @@
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -40939,7 +41059,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
       <c r="E18" s="10" t="inlineStr"/>
@@ -40979,7 +41099,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
       <c r="E19" s="10" t="inlineStr"/>
@@ -40997,7 +41117,7 @@
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -41037,7 +41157,7 @@
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -41059,7 +41179,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="10" t="inlineStr"/>
@@ -41077,7 +41197,7 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -41117,7 +41237,7 @@
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -41157,7 +41277,7 @@
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -41179,7 +41299,7 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
       <c r="E24" s="10" t="inlineStr"/>
@@ -41219,7 +41339,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="10" t="inlineStr"/>
@@ -41237,7 +41357,7 @@
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -41259,7 +41379,7 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="D26" s="10" t="inlineStr"/>
       <c r="E26" s="10" t="inlineStr"/>
@@ -41277,7 +41397,7 @@
         </is>
       </c>
       <c r="I26" s="9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -41317,7 +41437,7 @@
         </is>
       </c>
       <c r="I27" s="9" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -41379,7 +41499,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="D29" s="10" t="inlineStr"/>
       <c r="E29" s="10" t="inlineStr"/>
@@ -41397,7 +41517,7 @@
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -41437,7 +41557,7 @@
         </is>
       </c>
       <c r="I30" s="9" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -41459,7 +41579,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
       <c r="E31" s="10" t="inlineStr"/>
@@ -41477,7 +41597,7 @@
         </is>
       </c>
       <c r="I31" s="9" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
@@ -41499,7 +41619,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="D32" s="10" t="inlineStr"/>
       <c r="E32" s="10" t="inlineStr"/>
@@ -41517,7 +41637,7 @@
         </is>
       </c>
       <c r="I32" s="9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -41539,7 +41659,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="10" t="inlineStr"/>
@@ -41557,7 +41677,7 @@
         </is>
       </c>
       <c r="I33" s="9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -41597,7 +41717,7 @@
         </is>
       </c>
       <c r="I34" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -41659,7 +41779,7 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
@@ -41733,7 +41853,7 @@
         </is>
       </c>
       <c r="I37" s="9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -41833,7 +41953,7 @@
         </is>
       </c>
       <c r="I39" s="9" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -41859,7 +41979,7 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
@@ -41883,7 +42003,7 @@
         </is>
       </c>
       <c r="I40" s="9" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
@@ -41909,7 +42029,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
@@ -41933,7 +42053,7 @@
         </is>
       </c>
       <c r="I41" s="9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -42009,7 +42129,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
@@ -42017,7 +42137,7 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
@@ -42033,7 +42153,7 @@
         </is>
       </c>
       <c r="I43" s="9" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -42083,7 +42203,7 @@
         </is>
       </c>
       <c r="I44" s="9" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -42109,7 +42229,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
@@ -42133,7 +42253,7 @@
         </is>
       </c>
       <c r="I45" s="9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -42159,7 +42279,7 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
@@ -42209,7 +42329,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
@@ -42233,7 +42353,7 @@
         </is>
       </c>
       <c r="I47" s="9" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -42283,7 +42403,7 @@
         </is>
       </c>
       <c r="I48" s="9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -42309,7 +42429,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
@@ -42383,7 +42503,7 @@
         </is>
       </c>
       <c r="I50" s="9" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -42409,7 +42529,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
@@ -42433,7 +42553,7 @@
         </is>
       </c>
       <c r="I51" s="9" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -42483,7 +42603,7 @@
         </is>
       </c>
       <c r="I52" s="9" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -42509,7 +42629,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
@@ -42517,7 +42637,7 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>0.048</v>
+        <v>0.053</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
@@ -42533,7 +42653,7 @@
         </is>
       </c>
       <c r="I53" s="9" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -42583,7 +42703,7 @@
         </is>
       </c>
       <c r="I54" s="9" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
@@ -42627,13 +42747,13 @@
       <c r="G55" s="6" t="n">
         <v>0.053</v>
       </c>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I55" s="9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -42643,9 +42763,9 @@
       <c r="K55" s="6" t="n">
         <v>0.001</v>
       </c>
-      <c r="L55" s="8" t="inlineStr">
-        <is>
-          <t>Mala</t>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42683,7 +42803,7 @@
         </is>
       </c>
       <c r="I56" s="9" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -42709,7 +42829,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
@@ -42733,7 +42853,7 @@
         </is>
       </c>
       <c r="I57" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -42759,7 +42879,7 @@
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
@@ -42817,7 +42937,7 @@
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>0.037</v>
+        <v>0.047</v>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
@@ -42833,7 +42953,7 @@
         </is>
       </c>
       <c r="I59" s="9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -42883,7 +43003,7 @@
         </is>
       </c>
       <c r="I60" s="9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -42909,7 +43029,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
@@ -42983,7 +43103,7 @@
         </is>
       </c>
       <c r="I62" s="9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
@@ -43009,7 +43129,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
@@ -43033,7 +43153,7 @@
         </is>
       </c>
       <c r="I63" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
@@ -43083,7 +43203,7 @@
         </is>
       </c>
       <c r="I64" s="9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
@@ -43117,7 +43237,7 @@
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
@@ -43133,7 +43253,7 @@
         </is>
       </c>
       <c r="I65" s="9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
@@ -43183,7 +43303,7 @@
         </is>
       </c>
       <c r="I66" s="9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
@@ -43209,7 +43329,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
@@ -43233,7 +43353,7 @@
         </is>
       </c>
       <c r="I67" s="9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
@@ -43259,7 +43379,7 @@
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
@@ -43267,7 +43387,7 @@
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
@@ -43283,7 +43403,7 @@
         </is>
       </c>
       <c r="I68" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
